--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4285D8-47FE-45F1-98A7-BBF5E37B0E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE6F6BE-AF6A-4688-9644-D5E048B563EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2BB2E35B-3BDF-49BD-9CD5-4B0067813FC0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2BB2E35B-3BDF-49BD-9CD5-4B0067813FC0}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -314,57 +314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{BA083F51-FF15-48DA-8272-BCDEB28345F1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>【坐标、滚轴、向上取值，向下取值】
-第一次进入游戏时客户端显示的全局元素</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{3CAEC1D6-AC13-4BAD-AB41-DCEE08E6C216}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>【坐标、滚轴、向上取值，向下取值】
-第一次进入游戏时客户端显示的全局元素</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="2" shapeId="0" xr:uid="{9FF40D21-C413-46E6-9A78-AF644AF5353E}">
+    <comment ref="O1" authorId="2" shapeId="0" xr:uid="{9FF40D21-C413-46E6-9A78-AF644AF5353E}">
       <text>
         <r>
           <rPr>
@@ -390,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="1" shapeId="0" xr:uid="{6292A5A1-D37C-431A-A6E2-85727D77869D}">
+    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{6292A5A1-D37C-431A-A6E2-85727D77869D}">
       <text>
         <r>
           <rPr>
@@ -404,7 +354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="1" shapeId="0" xr:uid="{3D5B397E-0439-4400-B21F-3FA453F4CE29}">
+    <comment ref="S1" authorId="1" shapeId="0" xr:uid="{3D5B397E-0439-4400-B21F-3FA453F4CE29}">
       <text>
         <r>
           <rPr>
@@ -417,7 +367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{982000B2-20F4-48C3-A3B9-F5E1B6B6FBB9}">
+    <comment ref="T1" authorId="1" shapeId="0" xr:uid="{982000B2-20F4-48C3-A3B9-F5E1B6B6FBB9}">
       <text>
         <r>
           <rPr>
@@ -435,7 +385,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>游戏ID</t>
   </si>
@@ -470,9 +420,6 @@
     <t>游戏记录展示格子</t>
   </si>
   <si>
-    <t>初始格子</t>
-  </si>
-  <si>
     <t>分散使用格子</t>
   </si>
   <si>
@@ -511,9 +458,6 @@
     <t>[]</t>
   </si>
   <si>
-    <t>19:12:12:112:18:12:12:12:17:12:12:12:16:12:12:12:10:14:9:8</t>
-  </si>
-  <si>
     <t>美元快递</t>
   </si>
   <si>
@@ -599,18 +543,6 @@
   </si>
   <si>
     <t>winConditions</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>initialGrid</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>余额不足格子</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>notEnoughGrid</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1105,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4DB3DC-D774-4D0D-94BB-60E2E11E32A5}">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -1114,11 +1046,10 @@
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="11" max="11" width="14.625" customWidth="1"/>
     <col min="13" max="13" width="29.875" customWidth="1"/>
-    <col min="16" max="16" width="13.625" customWidth="1"/>
-    <col min="17" max="17" width="13.875" customWidth="1"/>
+    <col min="15" max="15" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="3" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="3" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1150,10 +1081,10 @@
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>9</v>
@@ -1165,151 +1096,133 @@
         <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" t="s">
         <v>37</v>
       </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>18</v>
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>51</v>
-      </c>
-      <c r="R3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>100100</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="E5" s="7">
         <v>1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5" s="7">
         <v>4</v>
@@ -1330,32 +1243,26 @@
         <v>100</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="R5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="P5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="8">
-        <v>1</v>
-      </c>
-      <c r="S5" s="8" t="s">
+      <c r="S5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="T5" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE6F6BE-AF6A-4688-9644-D5E048B563EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253FC843-62A4-4B72-A02C-E206E6EFC40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2BB2E35B-3BDF-49BD-9CD5-4B0067813FC0}"/>
+    <workbookView xWindow="31620" yWindow="1575" windowWidth="21600" windowHeight="11385" xr2:uid="{2BB2E35B-3BDF-49BD-9CD5-4B0067813FC0}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -498,10 +498,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>100100001:100100002:100100003:100100004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>List&lt;int&gt;{:}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -555,6 +551,10 @@
   </si>
   <si>
     <t>String</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100100101:100100102:100100103:100100104</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1081,10 +1081,10 @@
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>9</v>
@@ -1128,7 +1128,7 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -1149,10 +1149,10 @@
         <v>17</v>
       </c>
       <c r="M2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
         <v>17</v>
@@ -1178,31 +1178,31 @@
         <v>33</v>
       </c>
       <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>38</v>
       </c>
-      <c r="J3" t="s">
-        <v>39</v>
-      </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" t="s">
         <v>45</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>46</v>
-      </c>
-      <c r="P3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -1222,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G5" s="7">
         <v>4</v>
@@ -1243,7 +1243,7 @@
         <v>100</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N5" s="7" t="s">
         <v>22</v>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253FC843-62A4-4B72-A02C-E206E6EFC40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0070272A-EDEC-4DE7-A5BB-B10CD0F7401B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31620" yWindow="1575" windowWidth="21600" windowHeight="11385" xr2:uid="{2BB2E35B-3BDF-49BD-9CD5-4B0067813FC0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2BB2E35B-3BDF-49BD-9CD5-4B0067813FC0}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -1041,6 +1041,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="20.125" customWidth="1"/>
     <col min="3" max="3" width="13.625" customWidth="1"/>
     <col min="4" max="4" width="11.75" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0070272A-EDEC-4DE7-A5BB-B10CD0F7401B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A41C9F-5590-4E2D-85FF-64181D48FD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2BB2E35B-3BDF-49BD-9CD5-4B0067813FC0}"/>
   </bookViews>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -1,45 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A41C9F-5590-4E2D-85FF-64181D48FD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2BB2E35B-3BDF-49BD-9CD5-4B0067813FC0}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
     <author>Administrator</author>
     <author>po8zhaojinglei</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{E0FD00A4-CC69-4863-B4CF-6209B7F3BB2C}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -49,14 +50,13 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏的ID，唯一码</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{30732B48-42F9-410E-8936-FC249C4BD402}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -75,21 +74,19 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏名称，显示在大厅</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{AE4D4040-B487-4551-B43F-EE274F377C25}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -99,21 +96,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏Icon</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{0916686A-3E94-4431-AA63-40E3F2F699C0}">
+    <comment ref="E1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -122,7 +117,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -133,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{1EAE8288-CDFA-4749-8393-55C838E012E4}">
+    <comment ref="F1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -141,7 +135,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -151,7 +144,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -162,7 +154,6 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>如果该项目拥有神秘奖池时则需要在此项填写，奖池ID另配奖池专门的配置表
@@ -171,14 +162,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{DAB2DA3A-B384-4C85-932F-0B2FF46CEE05}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -188,21 +178,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏由多少行组成</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{BD72485D-E76E-455B-A9A7-A0EA6C3FBB3A}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -212,21 +200,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏由多少列组成</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{A41B2E8E-F089-4F09-8A9C-C682FB7E1083}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -236,21 +222,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>玩家进入游戏后，可以使用的最小线数</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{D742827A-3CDD-41B5-8CD6-9CF9BFDD8991}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -260,7 +244,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>玩家进入游戏后，可以使用的最大线数，最大线数和最小线数相同时，则说明不可选择
@@ -268,60 +251,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{54B0675F-E233-48F8-9CCA-C476C585B0E9}">
+    <comment ref="M1" authorId="2">
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>扩大单线押分值100倍</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{3FCA9370-61F5-4404-A2F4-C32CF4941F6C}">
-      <text>
-        <r>
-          <rPr>
             <b/>
             <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-倍数乘以总押分
-格式：[{奖励类型,倍数},{奖励类型,倍数},{奖励类型,倍数}]
-如：[{大奖,10}, {中奖,4},{小奖,2},{普通奖,0}]，则表示:
-普通(0,2)
-小奖[2,4)
-中奖[4,10)
-大奖[10,-∞)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="2" shapeId="0" xr:uid="{9FF40D21-C413-46E6-9A78-AF644AF5353E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
+            <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
           <t>po8zhaojinglei:</t>
@@ -330,7 +266,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -340,13 +275,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{6292A5A1-D37C-431A-A6E2-85727D77869D}">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0就是不会自动玩，24小时内可以继续玩免费和小游戏；超过24小时就会销毁没玩的免费和小游戏；
@@ -354,26 +288,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="1" shapeId="0" xr:uid="{3D5B397E-0439-4400-B21F-3FA453F4CE29}">
+    <comment ref="Q1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>分为无、货币类型、货币类型及押分，可后续添加；针对收集玩法</t>
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="1" shapeId="0" xr:uid="{982000B2-20F4-48C3-A3B9-F5E1B6B6FBB9}">
+    <comment ref="R1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>分为滚轴和结果库</t>
@@ -385,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t>游戏ID</t>
   </si>
@@ -393,6 +325,9 @@
     <t>名字</t>
   </si>
   <si>
+    <t>ENGNAME</t>
+  </si>
+  <si>
     <t>图标</t>
   </si>
   <si>
@@ -414,7 +349,7 @@
     <t>最大线数</t>
   </si>
   <si>
-    <t>中奖动画条件</t>
+    <t>额外投注倍率</t>
   </si>
   <si>
     <t>游戏记录展示格子</t>
@@ -439,11 +374,51 @@
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>engName</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>prizePoolIdList</t>
+  </si>
+  <si>
+    <t>rows</t>
+  </si>
+  <si>
+    <t>cols</t>
+  </si>
+  <si>
+    <t>minLine</t>
+  </si>
+  <si>
+    <t>maxLine</t>
+  </si>
+  <si>
+    <t>additionalBetRatio</t>
+  </si>
+  <si>
+    <t>distributeGrid</t>
+  </si>
+  <si>
+    <t>autoCompletion</t>
   </si>
   <si>
     <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
@@ -455,6 +430,9 @@
     <t>mykd</t>
   </si>
   <si>
+    <t>100100101:100100102:100100103:100100104</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -468,140 +446,203 @@
   </si>
   <si>
     <t>结果库</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ENGNAME</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>engName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>prizePoolIdList</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;{:}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rows</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>cols</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>minLine</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxLine</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外投注倍率</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>additionalBetRatio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>押分系数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>bettingCoefficient</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>超级大奖B,50;超级大奖A,30;大奖,20;中奖,10;小奖,5;普通奖,0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>winConditions</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>distributeGrid</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>autoCompletion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>String</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>100100101:100100102:100100103:100100104</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -609,32 +650,22 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -647,8 +678,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -671,9 +888,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -681,40 +1140,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -763,7 +1266,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -796,26 +1299,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -848,23 +1334,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1026,249 +1495,249 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4DB3DC-D774-4D0D-94BB-60E2E11E32A5}">
-  <dimension ref="A1:T5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="9" style="5"/>
+    <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="20.125" customWidth="1"/>
     <col min="3" max="3" width="13.625" customWidth="1"/>
     <col min="4" max="4" width="11.75" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="11" max="11" width="14.625" customWidth="1"/>
-    <col min="13" max="13" width="29.875" customWidth="1"/>
-    <col min="15" max="15" width="13.875" customWidth="1"/>
+    <col min="13" max="13" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:18">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="J3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:18">
+      <c r="A5" s="5">
+        <v>100100</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="6">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H5" s="6">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="I5" s="6">
+        <v>50</v>
+      </c>
+      <c r="J5" s="6">
+        <v>50</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="6"/>
+      <c r="N5" s="7">
+        <v>1</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="R5" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="M3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
-        <v>100100</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="7">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="7">
-        <v>4</v>
-      </c>
-      <c r="H5" s="7">
-        <v>5</v>
-      </c>
-      <c r="I5" s="7">
-        <v>50</v>
-      </c>
-      <c r="J5" s="7">
-        <v>50</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>100</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -31,7 +31,6 @@
   <authors>
     <author/>
     <author>Administrator</author>
-    <author>po8zhaojinglei</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0">
@@ -80,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="F1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -89,45 +88,23 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>游戏Icon</t>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1、【普通】 需要判断中奖线位置
+2、【满线】 不需要判断中奖线位置
+3、【普通消除】 需要判断中奖线位置，中奖后中奖图标消失，上方图案下落，继续判断是否中奖，依次循环，直至不中奖
+4、【满线消除】 不需要判断中奖线位置，中奖后中奖图标消失，上方图案下落，继续判断是否中奖，依次循环，直至不中奖</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1、普通
-2、满线
-3、普通消除
-4、满线消除</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="1">
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -159,50 +136,6 @@
           <t>如果该项目拥有神秘奖池时则需要在此项填写，奖池ID另配奖池专门的配置表
 ID1:ID2:ID3
 没有则填0</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>游戏由多少行组成</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>游戏由多少列组成</t>
         </r>
       </text>
     </comment>
@@ -224,7 +157,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>玩家进入游戏后，可以使用的最小线数</t>
+          <t>游戏由多少行组成</t>
         </r>
       </text>
     </comment>
@@ -246,12 +179,11 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>玩家进入游戏后，可以使用的最大线数，最大线数和最小线数相同时，则说明不可选择
-满线、满线消除类型的游戏这里都填1</t>
+          <t>游戏由多少列组成</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="2">
+    <comment ref="L1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -260,7 +192,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>po8zhaojinglei:</t>
+          <t>Administrator:</t>
         </r>
         <r>
           <rPr>
@@ -269,34 +201,95 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0代表使用之前分散格子，假如被替换，依然能计算
-1代表新分散格子，假如被替换，根据最新的格子进行结算
-</t>
+控制押分的系数</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0就是不会自动玩，24小时内可以继续玩免费和小游戏；超过24小时就会销毁没玩的免费和小游戏；
-1 就是15秒之后自动完成；</t>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Mr.M:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <strike/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>每条线使用的金币。满线时代替线数，总押分=单线押分值 X 使用线数</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+控制奖励的系数</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="1">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>分为无、货币类型、货币类型及押分，可后续添加；针对收集玩法</t>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Mr.M:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <strike/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">玩家进入游戏后，可以使用的最大线数，最大线数和最小线数相同时，则说明不可选择
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+满线、满线消除类型的游戏这里都填1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+总押分     = 单线押分 * 押分倍数 * 线注倍数 * 最大线数 
+</t>
         </r>
       </text>
     </comment>
@@ -304,11 +297,37 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>分为滚轴和结果库</t>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+总押分     = 单线押分 * 押分倍数 * 线注倍数 * 最大线数 
+总中奖金额 = 总押分 * 所有图案中奖倍数总和 ÷ 最大线数 ÷ 线注倍数
+总中奖金额 = 单线押分 * 押分倍数 * 所有图案中奖倍数总和
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>0就是不会自动玩，24小时内可以继续玩免费和小游戏；超过24小时就会销毁没玩的免费和小游戏；
+1 就是15秒之后自动完成；</t>
         </r>
       </text>
     </comment>
@@ -317,68 +336,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>游戏ID</t>
   </si>
   <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>ENGNAME</t>
-  </si>
-  <si>
-    <t>图标</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>奖池ID</t>
-  </si>
-  <si>
-    <t>行数</t>
-  </si>
-  <si>
-    <t>列数</t>
-  </si>
-  <si>
-    <t>最小线数</t>
+    <t>名字多语言ID</t>
+  </si>
+  <si>
+    <t>中奖线类型</t>
+  </si>
+  <si>
+    <t>消除类型</t>
+  </si>
+  <si>
+    <t>奖池规则ID</t>
+  </si>
+  <si>
+    <t>初始行数</t>
+  </si>
+  <si>
+    <t>初始列数</t>
+  </si>
+  <si>
+    <t>押分倍数</t>
+  </si>
+  <si>
+    <t>线注倍数</t>
   </si>
   <si>
     <t>最大线数</t>
   </si>
   <si>
-    <t>额外投注倍率</t>
-  </si>
-  <si>
-    <t>游戏记录展示格子</t>
-  </si>
-  <si>
-    <t>分散使用格子</t>
+    <t>单线押分</t>
+  </si>
+  <si>
+    <t>总押分</t>
+  </si>
+  <si>
+    <t>中奖倍率</t>
+  </si>
+  <si>
+    <t>中奖金额</t>
   </si>
   <si>
     <t>是否自动完成</t>
   </si>
   <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>jp赢奖方式</t>
-  </si>
-  <si>
-    <t>保存进度类型</t>
-  </si>
-  <si>
-    <t>RTP模式</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
@@ -388,10 +395,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>engName</t>
-  </si>
-  <si>
-    <t>icon</t>
+    <t>lineType</t>
   </si>
   <si>
     <t>type</t>
@@ -406,46 +410,43 @@
     <t>cols</t>
   </si>
   <si>
-    <t>minLine</t>
+    <t>betMultiple</t>
+  </si>
+  <si>
+    <t>lineMultiple</t>
   </si>
   <si>
     <t>maxLine</t>
   </si>
   <si>
-    <t>additionalBetRatio</t>
-  </si>
-  <si>
-    <t>distributeGrid</t>
-  </si>
-  <si>
     <t>autoCompletion</t>
   </si>
   <si>
-    <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
-  </si>
-  <si>
-    <t>&lt;&lt;"Dollars Express"/utf8&gt;&gt;</t>
-  </si>
-  <si>
-    <t>mykd</t>
-  </si>
-  <si>
-    <t>100100101:100100102:100100103:100100104</t>
-  </si>
-  <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>美元快递</t>
-  </si>
-  <si>
-    <t>小游戏</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>结果库</t>
+    <t>金矿大亨</t>
+  </si>
+  <si>
+    <t>需判断中奖线BaseLine表</t>
+  </si>
+  <si>
+    <t>不消除</t>
+  </si>
+  <si>
+    <t>4001001:4001002:4001003:4001004</t>
+  </si>
+  <si>
+    <t>用于计算坐标ID</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>满线,不需要走BaseLine表</t>
+  </si>
+  <si>
+    <t>中奖后消除</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
   </si>
 </sst>
 </file>
@@ -458,8 +459,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
-    <font>
+  <fonts count="32">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -484,11 +493,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -642,6 +657,18 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -653,19 +680,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -675,6 +696,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -987,32 +1014,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1021,149 +1039,182 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -1213,6 +1264,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1501,238 +1553,358 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="20.125" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
-    <col min="4" max="4" width="11.75" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="11" max="11" width="14.625" customWidth="1"/>
-    <col min="13" max="13" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="2" customWidth="1"/>
+    <col min="4" max="5" width="13.25" style="3" customWidth="1"/>
+    <col min="6" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="25" style="2" customWidth="1"/>
+    <col min="9" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="10.875" style="2" customWidth="1"/>
+    <col min="12" max="13" width="12.875" style="4" customWidth="1"/>
+    <col min="14" max="18" width="9" style="2"/>
+    <col min="19" max="19" width="14.125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:18">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:19">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="K1" s="5"/>
+      <c r="L1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="M1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="O1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="P1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="Q1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="R1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="B2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="I2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A3" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="15" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
+    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="15"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="6" t="s">
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A5" s="7">
+        <v>100100</v>
+      </c>
+      <c r="B5" s="7">
+        <v>100100008</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="H5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6" t="s">
+      <c r="I5" s="8">
+        <v>4</v>
+      </c>
+      <c r="J5" s="8">
+        <v>5</v>
+      </c>
+      <c r="K5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="L5" s="13">
+        <v>1</v>
+      </c>
+      <c r="M5" s="13">
+        <v>2</v>
+      </c>
+      <c r="N5" s="8">
+        <v>50</v>
+      </c>
+      <c r="O5" s="8">
+        <v>5000</v>
+      </c>
+      <c r="P5" s="8">
+        <f>N5*M5*L5*O5</f>
+        <v>500000</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>5</v>
+      </c>
+      <c r="R5" s="8">
+        <f>P5*Q5/N5/M5</f>
+        <v>25000</v>
+      </c>
+      <c r="S5" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A6" s="7">
+        <v>100700</v>
+      </c>
+      <c r="B6" s="7">
+        <v>100700000</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <v>4</v>
+      </c>
+      <c r="J6" s="8">
+        <v>4</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="13">
+        <v>1</v>
+      </c>
+      <c r="M6" s="13">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8">
+        <v>1</v>
+      </c>
+      <c r="O6" s="8">
+        <v>5000</v>
+      </c>
+      <c r="P6" s="8">
+        <f>N6*M6*L6*O6</f>
+        <v>5000</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>1</v>
+      </c>
+      <c r="R6" s="8">
+        <f>P6*Q6/N6/M6</f>
+        <v>5000</v>
+      </c>
+      <c r="S6" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:18">
-      <c r="A5" s="5">
-        <v>100100</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A7" s="7">
+        <v>101400</v>
+      </c>
+      <c r="B7" s="7">
+        <v>101400000</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="8">
+        <v>4014001</v>
+      </c>
+      <c r="I7" s="8">
+        <v>4</v>
+      </c>
+      <c r="J7" s="8">
+        <v>3</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="13">
         <v>1</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="6">
-        <v>4</v>
-      </c>
-      <c r="H5" s="6">
-        <v>5</v>
-      </c>
-      <c r="I5" s="6">
-        <v>50</v>
-      </c>
-      <c r="J5" s="6">
-        <v>50</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="7">
+      <c r="M7" s="13">
         <v>1</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>42</v>
+      <c r="N7" s="8">
+        <v>1</v>
+      </c>
+      <c r="O7" s="8">
+        <v>5000</v>
+      </c>
+      <c r="P7" s="8">
+        <f>N7*M7*L7*O7</f>
+        <v>5000</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>1</v>
+      </c>
+      <c r="R7" s="8">
+        <f>P7*Q7/N7/M7</f>
+        <v>5000</v>
+      </c>
+      <c r="S7" s="15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>游戏ID</t>
   </si>
@@ -386,6 +386,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>List&lt;int&gt;{|}</t>
+  </si>
+  <si>
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
@@ -431,19 +434,28 @@
     <t>不消除</t>
   </si>
   <si>
-    <t>4001001:4001002:4001003:4001004</t>
+    <t>100100101|100100102|100100103|100100104</t>
   </si>
   <si>
     <t>用于计算坐标ID</t>
   </si>
   <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>满线,不需要走BaseLine表</t>
+  </si>
+  <si>
+    <t>100300101|100300102|100300103|100300104</t>
+  </si>
+  <si>
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>满线,不需要走BaseLine表</t>
-  </si>
-  <si>
     <t>中奖后消除</t>
+  </si>
+  <si>
+    <t>财神</t>
   </si>
   <si>
     <t>埃及艳后</t>
@@ -459,7 +471,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,6 +507,13 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -650,6 +669,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -657,18 +682,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -680,6 +693,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -892,7 +911,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -912,6 +931,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1033,138 +1067,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1198,17 +1232,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1266,6 +1306,18 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1553,8 +1605,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="10.5" style="2" customWidth="1"/>
@@ -1596,25 +1648,25 @@
         <v>6</v>
       </c>
       <c r="K1" s="5"/>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="12" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="S1" s="5" t="s">
@@ -1647,11 +1699,11 @@
         <v>15</v>
       </c>
       <c r="K2" s="8"/>
-      <c r="L2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>16</v>
+      <c r="L2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>15</v>
@@ -1660,51 +1712,51 @@
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="8"/>
-      <c r="L3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="13" t="s">
+      <c r="L3" s="14" t="s">
         <v>25</v>
       </c>
+      <c r="M3" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="N3" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
-      <c r="S3" s="15" t="s">
-        <v>27</v>
+      <c r="S3" s="17" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="16.5" spans="1:19">
@@ -1719,14 +1771,14 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
-      <c r="S4" s="15"/>
+      <c r="S4" s="17"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A5" s="7">
@@ -1736,22 +1788,22 @@
         <v>100100008</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="10">
         <v>1</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8">
         <v>0</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="8">
         <v>4</v>
@@ -1759,155 +1811,294 @@
       <c r="J5" s="8">
         <v>5</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="13">
-        <v>1</v>
-      </c>
-      <c r="M5" s="13">
+      <c r="K5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="14">
+        <v>1</v>
+      </c>
+      <c r="M5" s="14">
         <v>2</v>
       </c>
       <c r="N5" s="8">
         <v>50</v>
       </c>
       <c r="O5" s="8">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="P5" s="8">
-        <f>N5*M5*L5*O5</f>
-        <v>500000</v>
+        <f t="shared" ref="P5:P9" si="0">N5*M5*L5*O5</f>
+        <v>100</v>
       </c>
       <c r="Q5" s="8">
         <v>5</v>
       </c>
       <c r="R5" s="8">
-        <f>P5*Q5/N5/M5</f>
-        <v>25000</v>
-      </c>
-      <c r="S5" s="15">
+        <f t="shared" ref="R5:R9" si="1">P5*Q5/N5/M5</f>
+        <v>5</v>
+      </c>
+      <c r="S5" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A6" s="7">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="B6" s="7">
-        <v>100700000</v>
+        <v>100300000</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="8">
         <v>0</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
       <c r="G6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="I6" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="8"/>
-      <c r="L6" s="13">
-        <v>1</v>
-      </c>
-      <c r="M6" s="13">
+      <c r="L6" s="14">
+        <v>1</v>
+      </c>
+      <c r="M6" s="14">
         <v>1</v>
       </c>
       <c r="N6" s="8">
         <v>1</v>
       </c>
       <c r="O6" s="8">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="P6" s="8">
-        <f>N6*M6*L6*O6</f>
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Q6" s="8">
         <v>1</v>
       </c>
       <c r="R6" s="8">
-        <f>P6*Q6/N6/M6</f>
-        <v>5000</v>
-      </c>
-      <c r="S6" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S6" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A7" s="7">
-        <v>101400</v>
+        <v>100700</v>
       </c>
       <c r="B7" s="7">
-        <v>101400000</v>
+        <v>100700000</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="10">
         <v>0</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="8">
         <v>0</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="8">
-        <v>4014001</v>
       </c>
       <c r="I7" s="8">
         <v>4</v>
       </c>
       <c r="J7" s="8">
+        <v>4</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="14">
+        <v>1</v>
+      </c>
+      <c r="M7" s="14">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8">
+        <v>15</v>
+      </c>
+      <c r="O7" s="8">
+        <v>1</v>
+      </c>
+      <c r="P7" s="8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>1</v>
+      </c>
+      <c r="R7" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S7" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A8" s="7">
+        <v>101200</v>
+      </c>
+      <c r="B8" s="7">
+        <v>101200000</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
         <v>3</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="13">
-        <v>1</v>
-      </c>
-      <c r="M7" s="13">
-        <v>1</v>
-      </c>
-      <c r="N7" s="8">
-        <v>1</v>
-      </c>
-      <c r="O7" s="8">
-        <v>5000</v>
-      </c>
-      <c r="P7" s="8">
-        <f>N7*M7*L7*O7</f>
-        <v>5000</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>1</v>
-      </c>
-      <c r="R7" s="8">
-        <f>P7*Q7/N7/M7</f>
-        <v>5000</v>
-      </c>
-      <c r="S7" s="15">
-        <v>1</v>
-      </c>
+      <c r="J8" s="8">
+        <v>5</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="14">
+        <v>1</v>
+      </c>
+      <c r="M8" s="14">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8">
+        <v>1</v>
+      </c>
+      <c r="O8" s="8">
+        <v>1</v>
+      </c>
+      <c r="P8" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>1</v>
+      </c>
+      <c r="R8" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S8" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A9" s="7">
+        <v>101400</v>
+      </c>
+      <c r="B9" s="7">
+        <v>101400000</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="8">
+        <v>101400101</v>
+      </c>
+      <c r="I9" s="8">
+        <v>4</v>
+      </c>
+      <c r="J9" s="8">
+        <v>3</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="14">
+        <v>1</v>
+      </c>
+      <c r="M9" s="14">
+        <v>1</v>
+      </c>
+      <c r="N9" s="8">
+        <v>1</v>
+      </c>
+      <c r="O9" s="8">
+        <v>1</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>1</v>
+      </c>
+      <c r="R9" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S9" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="10:10">
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" ht="16.5" spans="8:8">
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" ht="16.5" spans="8:8">
+      <c r="H21" s="11"/>
+    </row>
+    <row r="22" ht="16.5" spans="8:8">
+      <c r="H22" s="11"/>
+    </row>
+    <row r="23" ht="16.5" spans="8:8">
+      <c r="H23" s="11"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H23">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20:H22">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -1,45 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F00B03-4F47-441C-91C5-35080DA81AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -49,13 +43,14 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏的ID，唯一码</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -63,6 +58,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -73,19 +69,21 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏名称，显示在大厅</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -94,6 +92,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -104,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -112,6 +111,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -121,6 +121,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -131,6 +132,7 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>如果该项目拥有神秘奖池时则需要在此项填写，奖池ID另配奖池专门的配置表
@@ -139,13 +141,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -155,19 +158,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏由多少行组成</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -177,19 +182,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏由多少列组成</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -198,6 +205,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -205,13 +213,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -222,6 +231,7 @@
             <strike/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>每条线使用的金币。满线时代替线数，总押分=单线押分值 X 使用线数</t>
@@ -230,6 +240,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -237,13 +248,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -254,6 +266,7 @@
             <strike/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">玩家进入游戏后，可以使用的最大线数，最大线数和最小线数相同时，则说明不可选择
@@ -263,6 +276,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -270,13 +284,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="1">
+    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -285,6 +300,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -293,13 +309,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="1">
+    <comment ref="R1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -308,6 +325,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -318,12 +336,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="1">
+    <comment ref="S1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0就是不会自动玩，24小时内可以继续玩免费和小游戏；超过24小时就会销毁没玩的免费和小游戏；
@@ -336,7 +355,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>游戏ID</t>
   </si>
@@ -386,6 +405,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>List&lt;int&gt;{|}</t>
+  </si>
+  <si>
     <t>List&lt;int&gt;{:}</t>
   </si>
   <si>
@@ -431,19 +453,28 @@
     <t>不消除</t>
   </si>
   <si>
-    <t>4001001:4001002:4001003:4001004</t>
+    <t>100100101|100100102|100100103|100100104</t>
   </si>
   <si>
     <t>用于计算坐标ID</t>
   </si>
   <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>满线,不需要走BaseLine表</t>
+  </si>
+  <si>
+    <t>100300101|100300102|100300103|100300104</t>
+  </si>
+  <si>
     <t>麻将胡了</t>
   </si>
   <si>
-    <t>满线,不需要走BaseLine表</t>
-  </si>
-  <si>
     <t>中奖后消除</t>
+  </si>
+  <si>
+    <t>财神</t>
   </si>
   <si>
     <t>埃及艳后</t>
@@ -452,14 +483,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="32">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,30 +497,43 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -503,173 +541,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -677,16 +556,53 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -705,194 +621,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -917,252 +647,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1174,16 +677,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1192,84 +692,64 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1547,369 +1027,508 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="10.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="2" customWidth="1"/>
-    <col min="4" max="5" width="13.25" style="3" customWidth="1"/>
+    <col min="3" max="4" width="13.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.125" style="2" customWidth="1"/>
     <col min="6" max="7" width="9" style="2"/>
     <col min="8" max="8" width="25" style="2" customWidth="1"/>
     <col min="9" max="10" width="9" style="2"/>
     <col min="11" max="11" width="10.875" style="2" customWidth="1"/>
-    <col min="12" max="13" width="12.875" style="4" customWidth="1"/>
+    <col min="12" max="13" width="12.875" style="3" customWidth="1"/>
     <col min="14" max="18" width="9" style="2"/>
     <col min="19" max="19" width="14.125" style="2" customWidth="1"/>
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:19">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="21.95" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="11" t="s">
+      <c r="K1" s="4"/>
+      <c r="L1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:19" s="1" customFormat="1" ht="16.5">
+      <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="7"/>
+      <c r="H2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="8" t="s">
+      <c r="K2" s="7"/>
+      <c r="L2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
       <c r="S2" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:19" s="1" customFormat="1" ht="16.5">
+      <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="10" t="s">
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="8" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="13" t="s">
+      <c r="J3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="K3" s="7"/>
+      <c r="L3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="M3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
+      <c r="N3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
       <c r="S3" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
+    <row r="4" spans="1:19" s="1" customFormat="1" ht="16.5">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
       <c r="S4" s="15"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="7">
+    <row r="5" spans="1:19" s="1" customFormat="1" ht="16.5">
+      <c r="A5" s="6">
         <v>100100</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>100100008</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="8">
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="7">
         <v>0</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="8">
+      <c r="H5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="7">
         <v>4</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="7">
         <v>5</v>
       </c>
-      <c r="K5" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="13">
-        <v>1</v>
-      </c>
-      <c r="M5" s="13">
+      <c r="K5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="12">
+        <v>1</v>
+      </c>
+      <c r="M5" s="12">
         <v>2</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="7">
         <v>50</v>
       </c>
-      <c r="O5" s="8">
-        <v>5000</v>
-      </c>
-      <c r="P5" s="8">
-        <f>N5*M5*L5*O5</f>
-        <v>500000</v>
-      </c>
-      <c r="Q5" s="8">
+      <c r="O5" s="7">
+        <v>1</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" ref="P5:P8" si="0">N5*M5*L5*O5</f>
+        <v>100</v>
+      </c>
+      <c r="Q5" s="7">
         <v>5</v>
       </c>
-      <c r="R5" s="8">
-        <f>P5*Q5/N5/M5</f>
-        <v>25000</v>
+      <c r="R5" s="7">
+        <f t="shared" ref="R5:R8" si="1">P5*Q5/N5/M5</f>
+        <v>5</v>
       </c>
       <c r="S5" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="7">
+    <row r="6" spans="1:19" s="1" customFormat="1" ht="16.5">
+      <c r="A6" s="6">
+        <v>100300</v>
+      </c>
+      <c r="B6" s="6">
+        <v>100300000</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="7">
+        <v>3</v>
+      </c>
+      <c r="J6" s="7">
+        <v>3</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="12">
+        <v>1</v>
+      </c>
+      <c r="M6" s="12">
+        <v>1</v>
+      </c>
+      <c r="N6" s="7">
+        <v>1</v>
+      </c>
+      <c r="O6" s="7">
+        <v>1</v>
+      </c>
+      <c r="P6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>1</v>
+      </c>
+      <c r="R6" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="1" customFormat="1" ht="16.5">
+      <c r="A7" s="6">
         <v>100700</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B7" s="6">
         <v>100700000</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="8">
         <v>0</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="8">
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="7">
         <v>0</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I7" s="7">
         <v>4</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J7" s="7">
+        <v>5</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="12">
+        <v>1</v>
+      </c>
+      <c r="M7" s="12">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7">
+        <v>15</v>
+      </c>
+      <c r="O7" s="7">
+        <v>1</v>
+      </c>
+      <c r="P7" s="7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>1</v>
+      </c>
+      <c r="R7" s="7">
+        <f>P7*Q7/N7/M7</f>
+        <v>1</v>
+      </c>
+      <c r="S7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="1" customFormat="1" ht="16.5">
+      <c r="A8" s="6">
+        <v>101200</v>
+      </c>
+      <c r="B8" s="6">
+        <v>101200000</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>3</v>
+      </c>
+      <c r="J8" s="7">
+        <v>5</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="12">
+        <v>1</v>
+      </c>
+      <c r="M8" s="12">
+        <v>1</v>
+      </c>
+      <c r="N8" s="7">
+        <v>1</v>
+      </c>
+      <c r="O8" s="7">
+        <v>1</v>
+      </c>
+      <c r="P8" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>1</v>
+      </c>
+      <c r="R8" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" s="1" customFormat="1" ht="16.5">
+      <c r="A9" s="6">
+        <v>101400</v>
+      </c>
+      <c r="B9" s="6">
+        <v>101400000</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="7">
+        <v>101400101</v>
+      </c>
+      <c r="I9" s="7">
         <v>4</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="13">
-        <v>1</v>
-      </c>
-      <c r="M6" s="13">
-        <v>1</v>
-      </c>
-      <c r="N6" s="8">
-        <v>1</v>
-      </c>
-      <c r="O6" s="8">
-        <v>5000</v>
-      </c>
-      <c r="P6" s="8">
-        <f>N6*M6*L6*O6</f>
-        <v>5000</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>1</v>
-      </c>
-      <c r="R6" s="8">
-        <f>P6*Q6/N6/M6</f>
-        <v>5000</v>
-      </c>
-      <c r="S6" s="15">
+      <c r="J9" s="7">
+        <v>3</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="12">
+        <v>1</v>
+      </c>
+      <c r="M9" s="12">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7">
+        <v>1</v>
+      </c>
+      <c r="O9" s="7">
+        <v>1</v>
+      </c>
+      <c r="P9" s="7">
+        <f>N9*M9*L9*O9</f>
+        <v>1</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>1</v>
+      </c>
+      <c r="R9" s="7">
+        <f>P9*Q9/N9/M9</f>
+        <v>1</v>
+      </c>
+      <c r="S9" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="7">
-        <v>101400</v>
-      </c>
-      <c r="B7" s="7">
-        <v>101400000</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="8">
-        <v>4014001</v>
-      </c>
-      <c r="I7" s="8">
-        <v>4</v>
-      </c>
-      <c r="J7" s="8">
-        <v>3</v>
-      </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="13">
-        <v>1</v>
-      </c>
-      <c r="M7" s="13">
-        <v>1</v>
-      </c>
-      <c r="N7" s="8">
-        <v>1</v>
-      </c>
-      <c r="O7" s="8">
-        <v>5000</v>
-      </c>
-      <c r="P7" s="8">
-        <f>N7*M7*L7*O7</f>
-        <v>5000</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>1</v>
-      </c>
-      <c r="R7" s="8">
-        <f>P7*Q7/N7/M7</f>
-        <v>5000</v>
-      </c>
-      <c r="S7" s="15">
-        <v>1</v>
-      </c>
+    <row r="19" spans="8:10">
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="8:10" ht="16.5">
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="8:10" ht="16.5">
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="8:10" ht="16.5">
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" spans="8:10" ht="16.5">
+      <c r="H23" s="9"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <conditionalFormatting sqref="H20:H22">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -1,39 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F00B03-4F47-441C-91C5-35080DA81AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -43,14 +49,13 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏的ID，唯一码</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -58,7 +63,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -69,21 +73,19 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏名称，显示在大厅</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -92,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -103,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -111,7 +112,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -121,7 +121,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -132,7 +131,6 @@
             <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>如果该项目拥有神秘奖池时则需要在此项填写，奖池ID另配奖池专门的配置表
@@ -141,14 +139,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -158,21 +155,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏由多少行组成</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -182,21 +177,19 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏由多少列组成</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="L1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -205,7 +198,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -213,14 +205,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -231,7 +222,6 @@
             <strike/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>每条线使用的金币。满线时代替线数，总押分=单线押分值 X 使用线数</t>
@@ -240,7 +230,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -248,14 +237,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -266,7 +254,6 @@
             <strike/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">玩家进入游戏后，可以使用的最大线数，最大线数和最小线数相同时，则说明不可选择
@@ -276,7 +263,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -284,14 +270,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="P1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -300,7 +285,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -309,14 +293,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="R1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -325,7 +308,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -336,13 +318,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="S1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0就是不会自动玩，24小时内可以继续玩免费和小游戏；超过24小时就会销毁没玩的免费和小游戏；
@@ -483,8 +464,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +484,24 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -526,14 +509,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -541,14 +522,167 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -556,53 +690,22 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <strike/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -621,8 +724,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -660,14 +949,256 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -677,13 +1208,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -692,10 +1226,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -717,21 +1254,59 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -747,9 +1322,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1027,508 +1599,508 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="10.5" style="2" customWidth="1"/>
-    <col min="3" max="4" width="13.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="2" customWidth="1"/>
+    <col min="4" max="5" width="13.25" style="3" customWidth="1"/>
     <col min="6" max="7" width="9" style="2"/>
     <col min="8" max="8" width="25" style="2" customWidth="1"/>
     <col min="9" max="10" width="9" style="2"/>
     <col min="11" max="11" width="10.875" style="2" customWidth="1"/>
-    <col min="12" max="13" width="12.875" style="3" customWidth="1"/>
+    <col min="12" max="13" width="12.875" style="4" customWidth="1"/>
     <col min="14" max="18" width="9" style="2"/>
     <col min="19" max="19" width="14.125" style="2" customWidth="1"/>
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="21.95" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:19">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="10" t="s">
+      <c r="K1" s="5"/>
+      <c r="L1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="1" customFormat="1" ht="16.5">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="9"/>
+      <c r="F2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
+      <c r="G2" s="8"/>
+      <c r="H2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="12" t="s">
+      <c r="K2" s="8"/>
+      <c r="L2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="15" t="s">
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="1" customFormat="1" ht="16.5">
-      <c r="A3" s="6" t="s">
+    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="8"/>
+      <c r="H3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="12" t="s">
+      <c r="K3" s="8"/>
+      <c r="L3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="15" t="s">
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="1" customFormat="1" ht="16.5">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="15"/>
+    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="17"/>
     </row>
-    <row r="5" spans="1:19" s="1" customFormat="1" ht="16.5">
-      <c r="A5" s="6">
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A5" s="7">
         <v>100100</v>
       </c>
-      <c r="B5" s="6">
-        <v>100100008</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="7">
+        <v>100100026</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="8">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>0</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="8">
         <v>4</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="8">
         <v>5</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="12">
-        <v>1</v>
-      </c>
-      <c r="M5" s="12">
+      <c r="L5" s="14">
+        <v>1</v>
+      </c>
+      <c r="M5" s="14">
         <v>2</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="8">
         <v>50</v>
       </c>
-      <c r="O5" s="7">
-        <v>1</v>
-      </c>
-      <c r="P5" s="7">
-        <f t="shared" ref="P5:P8" si="0">N5*M5*L5*O5</f>
+      <c r="O5" s="8">
+        <v>1</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" ref="P5:P9" si="0">N5*M5*L5*O5</f>
         <v>100</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q5" s="8">
         <v>5</v>
       </c>
-      <c r="R5" s="7">
-        <f t="shared" ref="R5:R8" si="1">P5*Q5/N5/M5</f>
+      <c r="R5" s="8">
+        <f t="shared" ref="R5:R9" si="1">P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
-      <c r="S5" s="15">
+      <c r="S5" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="1" customFormat="1" ht="16.5">
-      <c r="A6" s="6">
+    <row r="6" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A6" s="7">
         <v>100300</v>
       </c>
-      <c r="B6" s="6">
-        <v>100300000</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="7">
+        <v>100300001</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="8">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="8">
         <v>3</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="8">
         <v>3</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="12">
-        <v>1</v>
-      </c>
-      <c r="M6" s="12">
-        <v>1</v>
-      </c>
-      <c r="N6" s="7">
-        <v>1</v>
-      </c>
-      <c r="O6" s="7">
-        <v>1</v>
-      </c>
-      <c r="P6" s="7">
+      <c r="K6" s="8"/>
+      <c r="L6" s="14">
+        <v>1</v>
+      </c>
+      <c r="M6" s="14">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8">
+        <v>1</v>
+      </c>
+      <c r="O6" s="8">
+        <v>1</v>
+      </c>
+      <c r="P6" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q6" s="7">
-        <v>1</v>
-      </c>
-      <c r="R6" s="7">
+      <c r="Q6" s="8">
+        <v>1</v>
+      </c>
+      <c r="R6" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="1" customFormat="1" ht="16.5">
-      <c r="A7" s="6">
+    <row r="7" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A7" s="7">
         <v>100700</v>
       </c>
-      <c r="B7" s="6">
-        <v>100700000</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="7">
+        <v>100700001</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="10">
         <v>0</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <v>0</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="8">
         <v>4</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="8">
         <v>5</v>
       </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="12">
-        <v>1</v>
-      </c>
-      <c r="M7" s="12">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7">
+      <c r="K7" s="8"/>
+      <c r="L7" s="14">
+        <v>1</v>
+      </c>
+      <c r="M7" s="14">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8">
+        <v>1</v>
+      </c>
+      <c r="O7" s="8">
+        <v>1</v>
+      </c>
+      <c r="P7" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>1</v>
+      </c>
+      <c r="R7" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S7" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A8" s="7">
+        <v>101200</v>
+      </c>
+      <c r="B8" s="7">
+        <v>101200001</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <v>3</v>
+      </c>
+      <c r="J8" s="8">
+        <v>5</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="14">
+        <v>1</v>
+      </c>
+      <c r="M8" s="14">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8">
         <v>15</v>
       </c>
-      <c r="O7" s="7">
-        <v>1</v>
-      </c>
-      <c r="P7" s="7">
+      <c r="O8" s="8">
+        <v>1</v>
+      </c>
+      <c r="P8" s="8">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q7" s="7">
-        <v>1</v>
-      </c>
-      <c r="R7" s="7">
-        <f>P7*Q7/N7/M7</f>
-        <v>1</v>
-      </c>
-      <c r="S7" s="15">
+      <c r="Q8" s="8">
+        <v>1</v>
+      </c>
+      <c r="R8" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S8" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="1" customFormat="1" ht="16.5">
-      <c r="A8" s="6">
-        <v>101200</v>
-      </c>
-      <c r="B8" s="6">
-        <v>101200000</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8" t="s">
+    <row r="9" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A9" s="7">
+        <v>101400</v>
+      </c>
+      <c r="B9" s="7">
+        <v>101400001</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F9" s="8">
         <v>0</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="7">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7">
+      <c r="H9" s="8">
+        <v>101400101</v>
+      </c>
+      <c r="I9" s="8">
+        <v>4</v>
+      </c>
+      <c r="J9" s="8">
         <v>3</v>
       </c>
-      <c r="J8" s="7">
-        <v>5</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="12">
-        <v>1</v>
-      </c>
-      <c r="M8" s="12">
-        <v>1</v>
-      </c>
-      <c r="N8" s="7">
-        <v>1</v>
-      </c>
-      <c r="O8" s="7">
-        <v>1</v>
-      </c>
-      <c r="P8" s="7">
+      <c r="K9" s="8"/>
+      <c r="L9" s="14">
+        <v>1</v>
+      </c>
+      <c r="M9" s="14">
+        <v>1</v>
+      </c>
+      <c r="N9" s="8">
+        <v>1</v>
+      </c>
+      <c r="O9" s="8">
+        <v>1</v>
+      </c>
+      <c r="P9" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="7">
-        <v>1</v>
-      </c>
-      <c r="R8" s="7">
+      <c r="Q9" s="8">
+        <v>1</v>
+      </c>
+      <c r="R9" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S9" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="1" customFormat="1" ht="16.5">
-      <c r="A9" s="6">
-        <v>101400</v>
-      </c>
-      <c r="B9" s="6">
-        <v>101400000</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="7">
-        <v>101400101</v>
-      </c>
-      <c r="I9" s="7">
-        <v>4</v>
-      </c>
-      <c r="J9" s="7">
-        <v>3</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="12">
-        <v>1</v>
-      </c>
-      <c r="M9" s="12">
-        <v>1</v>
-      </c>
-      <c r="N9" s="7">
-        <v>1</v>
-      </c>
-      <c r="O9" s="7">
-        <v>1</v>
-      </c>
-      <c r="P9" s="7">
-        <f>N9*M9*L9*O9</f>
-        <v>1</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>1</v>
-      </c>
-      <c r="R9" s="7">
-        <f>P9*Q9/N9/M9</f>
-        <v>1</v>
-      </c>
-      <c r="S9" s="15">
-        <v>1</v>
-      </c>
+    <row r="19" spans="10:10">
+      <c r="J19" s="16"/>
     </row>
-    <row r="19" spans="8:10">
-      <c r="J19" s="14"/>
+    <row r="20" ht="16.5" spans="8:8">
+      <c r="H20" s="11"/>
     </row>
-    <row r="20" spans="8:10" ht="16.5">
-      <c r="H20" s="9"/>
+    <row r="21" ht="16.5" spans="8:8">
+      <c r="H21" s="11"/>
     </row>
-    <row r="21" spans="8:10" ht="16.5">
-      <c r="H21" s="9"/>
+    <row r="22" ht="16.5" spans="8:8">
+      <c r="H22" s="11"/>
     </row>
-    <row r="22" spans="8:10" ht="16.5">
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="8:10" ht="16.5">
-      <c r="H23" s="9"/>
+    <row r="23" ht="16.5" spans="8:8">
+      <c r="H23" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
-  <conditionalFormatting sqref="H20:H22">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H23">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H20:H22">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -675,17 +675,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -694,13 +683,24 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1939,21 +1939,21 @@
         <v>1</v>
       </c>
       <c r="N7" s="8">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O7" s="8">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q7" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="S7" s="17">
         <v>1</v>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -669,8 +669,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -682,13 +682,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2057,21 +2057,21 @@
         <v>1</v>
       </c>
       <c r="N9" s="8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O9" s="8">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="P9" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R9" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="S9" s="17">
         <v>1</v>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>游戏ID</t>
   </si>
@@ -459,6 +459,12 @@
   </si>
   <si>
     <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>财富银行</t>
+  </si>
+  <si>
+    <t>102400101|102400102|102400103|102400104</t>
   </si>
 </sst>
 </file>
@@ -669,8 +675,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -682,25 +694,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1613,7 +1619,7 @@
     <col min="3" max="3" width="13.25" style="2" customWidth="1"/>
     <col min="4" max="5" width="13.25" style="3" customWidth="1"/>
     <col min="6" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="51.125" style="2" customWidth="1"/>
     <col min="9" max="10" width="9" style="2"/>
     <col min="11" max="11" width="10.875" style="2" customWidth="1"/>
     <col min="12" max="13" width="12.875" style="4" customWidth="1"/>
@@ -1827,14 +1833,14 @@
         <v>1</v>
       </c>
       <c r="P5" s="8">
-        <f t="shared" ref="P5:P9" si="0">N5*M5*L5*O5</f>
+        <f t="shared" ref="P5:P10" si="0">N5*M5*L5*O5</f>
         <v>100</v>
       </c>
       <c r="Q5" s="8">
         <v>5</v>
       </c>
       <c r="R5" s="8">
-        <f t="shared" ref="R5:R9" si="1">P5*Q5/N5/M5</f>
+        <f t="shared" ref="R5:R10" si="1">P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
       <c r="S5" s="17">
@@ -2074,6 +2080,67 @@
         <v>0.3</v>
       </c>
       <c r="S9" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A10" s="7">
+        <v>102400</v>
+      </c>
+      <c r="B10" s="7">
+        <v>102400026</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="8">
+        <v>4</v>
+      </c>
+      <c r="J10" s="8">
+        <v>5</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="14">
+        <v>1</v>
+      </c>
+      <c r="M10" s="14">
+        <v>2</v>
+      </c>
+      <c r="N10" s="8">
+        <v>50</v>
+      </c>
+      <c r="O10" s="8">
+        <v>1</v>
+      </c>
+      <c r="P10" s="8">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>5</v>
+      </c>
+      <c r="R10" s="8">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="S10" s="17">
         <v>1</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>游戏ID</t>
   </si>
@@ -465,6 +465,18 @@
   </si>
   <si>
     <t>102400101|102400102|102400103|102400104</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>101700101|101700102|101700103|101700104</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>102200101|102200102|102200103|102200104</t>
   </si>
 </sst>
 </file>
@@ -486,6 +498,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -499,12 +517,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -514,19 +539,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -675,14 +687,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <strike/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -694,18 +706,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1204,60 +1216,69 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1614,550 +1635,667 @@
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="10.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="2" customWidth="1"/>
-    <col min="4" max="5" width="13.25" style="3" customWidth="1"/>
-    <col min="6" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="51.125" style="2" customWidth="1"/>
-    <col min="9" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="10.875" style="2" customWidth="1"/>
-    <col min="12" max="13" width="12.875" style="4" customWidth="1"/>
-    <col min="14" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="14.125" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="10.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="3" customWidth="1"/>
+    <col min="4" max="5" width="13.25" style="4" customWidth="1"/>
+    <col min="6" max="7" width="9" style="3"/>
+    <col min="8" max="8" width="51.125" style="3" customWidth="1"/>
+    <col min="9" max="10" width="9" style="3"/>
+    <col min="11" max="11" width="10.875" style="3" customWidth="1"/>
+    <col min="12" max="13" width="12.875" style="5" customWidth="1"/>
+    <col min="14" max="18" width="9" style="3"/>
+    <col min="19" max="19" width="14.125" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:19">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="7"/>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="12" t="s">
+      <c r="K1" s="6"/>
+      <c r="L1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="14" t="s">
+      <c r="K2" s="11"/>
+      <c r="L2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="17" t="s">
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="15"/>
+      <c r="F3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8" t="s">
+      <c r="G3" s="11"/>
+      <c r="H3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="14" t="s">
+      <c r="K3" s="11"/>
+      <c r="L3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="17" t="s">
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="17"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="14"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="7">
+      <c r="A5" s="10">
         <v>100100</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>100100026</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="10">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="11">
         <v>0</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="11">
         <v>4</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="11">
         <v>5</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="14">
-        <v>1</v>
-      </c>
-      <c r="M5" s="14">
+      <c r="L5" s="13">
+        <v>1</v>
+      </c>
+      <c r="M5" s="13">
         <v>2</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="11">
         <v>50</v>
       </c>
-      <c r="O5" s="8">
-        <v>1</v>
-      </c>
-      <c r="P5" s="8">
-        <f t="shared" ref="P5:P10" si="0">N5*M5*L5*O5</f>
+      <c r="O5" s="11">
+        <v>1</v>
+      </c>
+      <c r="P5" s="11">
+        <f t="shared" ref="P5:P12" si="0">N5*M5*L5*O5</f>
         <v>100</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="11">
         <v>5</v>
       </c>
-      <c r="R5" s="8">
-        <f t="shared" ref="R5:R10" si="1">P5*Q5/N5/M5</f>
+      <c r="R5" s="11">
+        <f t="shared" ref="R5:R12" si="1">P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
-      <c r="S5" s="17">
+      <c r="S5" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="7">
+      <c r="A6" s="10">
         <v>100300</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <v>100300001</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="10">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="15">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="11">
         <v>0</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="11">
         <v>3</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="11">
         <v>3</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="14">
-        <v>1</v>
-      </c>
-      <c r="M6" s="14">
-        <v>1</v>
-      </c>
-      <c r="N6" s="8">
-        <v>1</v>
-      </c>
-      <c r="O6" s="8">
-        <v>1</v>
-      </c>
-      <c r="P6" s="8">
+      <c r="K6" s="11"/>
+      <c r="L6" s="13">
+        <v>1</v>
+      </c>
+      <c r="M6" s="13">
+        <v>1</v>
+      </c>
+      <c r="N6" s="11">
+        <v>1</v>
+      </c>
+      <c r="O6" s="11">
+        <v>1</v>
+      </c>
+      <c r="P6" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q6" s="8">
-        <v>1</v>
-      </c>
-      <c r="R6" s="8">
+      <c r="Q6" s="11">
+        <v>1</v>
+      </c>
+      <c r="R6" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S6" s="17">
+      <c r="S6" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="7">
+      <c r="A7" s="10">
         <v>100700</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <v>100700001</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="15">
         <v>0</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="11">
+        <v>1</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="11">
         <v>0</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="11">
         <v>4</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="11">
         <v>5</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="14">
-        <v>1</v>
-      </c>
-      <c r="M7" s="14">
-        <v>1</v>
-      </c>
-      <c r="N7" s="8">
+      <c r="K7" s="11"/>
+      <c r="L7" s="13">
+        <v>1</v>
+      </c>
+      <c r="M7" s="13">
+        <v>1</v>
+      </c>
+      <c r="N7" s="11">
         <v>20</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="11">
         <v>0.05</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="11">
         <v>2</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="11">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="S7" s="17">
+      <c r="S7" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A8" s="7">
+      <c r="A8" s="10">
         <v>101200</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>101200001</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="10">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="15">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="11">
         <v>0</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="11">
         <v>0</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="11">
         <v>3</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="11">
         <v>5</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="14">
-        <v>1</v>
-      </c>
-      <c r="M8" s="14">
-        <v>1</v>
-      </c>
-      <c r="N8" s="8">
+      <c r="K8" s="11"/>
+      <c r="L8" s="13">
+        <v>1</v>
+      </c>
+      <c r="M8" s="13">
+        <v>1</v>
+      </c>
+      <c r="N8" s="11">
         <v>15</v>
       </c>
-      <c r="O8" s="8">
-        <v>1</v>
-      </c>
-      <c r="P8" s="8">
+      <c r="O8" s="11">
+        <v>1</v>
+      </c>
+      <c r="P8" s="11">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q8" s="8">
-        <v>1</v>
-      </c>
-      <c r="R8" s="8">
+      <c r="Q8" s="11">
+        <v>1</v>
+      </c>
+      <c r="R8" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S8" s="17">
+      <c r="S8" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A9" s="7">
+      <c r="A9" s="10">
         <v>101400</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <v>101400001</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="15">
         <v>0</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="11">
         <v>0</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="11">
         <v>101400101</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="11">
         <v>4</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="11">
         <v>3</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="14">
-        <v>1</v>
-      </c>
-      <c r="M9" s="14">
-        <v>1</v>
-      </c>
-      <c r="N9" s="8">
+      <c r="K9" s="11"/>
+      <c r="L9" s="13">
+        <v>1</v>
+      </c>
+      <c r="M9" s="13">
+        <v>1</v>
+      </c>
+      <c r="N9" s="11">
         <v>10</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="11">
         <v>0.05</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="11">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="11">
         <v>6</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="S9" s="17">
+      <c r="S9" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="7">
+      <c r="A10" s="10">
         <v>102400</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>102400026</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="15">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="11">
         <v>0</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="11">
         <v>4</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="11">
         <v>5</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="14">
-        <v>1</v>
-      </c>
-      <c r="M10" s="14">
+      <c r="L10" s="13">
+        <v>1</v>
+      </c>
+      <c r="M10" s="13">
         <v>2</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="11">
         <v>50</v>
       </c>
-      <c r="O10" s="8">
-        <v>1</v>
-      </c>
-      <c r="P10" s="8">
+      <c r="O10" s="11">
+        <v>1</v>
+      </c>
+      <c r="P10" s="11">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q10" s="11">
         <v>5</v>
       </c>
-      <c r="R10" s="8">
+      <c r="R10" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="S10" s="17">
+      <c r="S10" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="10:10">
-      <c r="J19" s="16"/>
+    <row r="11" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A11" s="10">
+        <v>101700</v>
+      </c>
+      <c r="B11" s="10">
+        <v>101700001</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="11">
+        <v>4</v>
+      </c>
+      <c r="J11" s="11">
+        <v>5</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="13">
+        <v>1</v>
+      </c>
+      <c r="M11" s="13">
+        <v>1</v>
+      </c>
+      <c r="N11" s="11">
+        <v>20</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="P11" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>2</v>
+      </c>
+      <c r="R11" s="11">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="S11" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" ht="16.5" spans="8:8">
-      <c r="H20" s="11"/>
+    <row r="12" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A12" s="2">
+        <v>102200</v>
+      </c>
+      <c r="B12" s="2">
+        <v>102200001</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="2">
+        <v>3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5</v>
+      </c>
+      <c r="L12" s="18">
+        <v>1</v>
+      </c>
+      <c r="M12" s="18">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2">
+        <v>25</v>
+      </c>
+      <c r="O12" s="11">
+        <v>1</v>
+      </c>
+      <c r="P12" s="11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>1</v>
+      </c>
+      <c r="R12" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S12" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" ht="16.5" spans="8:8">
-      <c r="H21" s="11"/>
+    <row r="19" spans="8:10">
+      <c r="J19" s="19"/>
     </row>
-    <row r="22" ht="16.5" spans="8:8">
-      <c r="H22" s="11"/>
+    <row r="20" ht="16.5" spans="8:10">
+      <c r="H20" s="20"/>
     </row>
-    <row r="23" ht="16.5" spans="8:8">
-      <c r="H23" s="11"/>
+    <row r="21" ht="16.5" spans="8:10">
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" ht="16.5" spans="8:10">
+      <c r="H22" s="20"/>
+    </row>
+    <row r="23" ht="16.5" spans="8:10">
+      <c r="H23" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H23">

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>游戏ID</t>
   </si>
@@ -477,6 +477,12 @@
   </si>
   <si>
     <t>102200101|102200102|102200103|102200104</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>102100101|102100102|102100103|102100104</t>
   </si>
 </sst>
 </file>
@@ -687,13 +693,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <strike/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -706,18 +723,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1216,7 +1222,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1267,9 +1273,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1854,14 +1857,14 @@
         <v>1</v>
       </c>
       <c r="P5" s="11">
-        <f t="shared" ref="P5:P12" si="0">N5*M5*L5*O5</f>
+        <f t="shared" ref="P5:P13" si="0">N5*M5*L5*O5</f>
         <v>100</v>
       </c>
       <c r="Q5" s="11">
         <v>5</v>
       </c>
       <c r="R5" s="11">
-        <f t="shared" ref="R5:R12" si="1">P5*Q5/N5/M5</f>
+        <f t="shared" ref="R5:R13" si="1">P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
       <c r="S5" s="14">
@@ -2231,7 +2234,7 @@
       <c r="B12" s="2">
         <v>102200001</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="15">
@@ -2255,10 +2258,10 @@
       <c r="J12" s="2">
         <v>5</v>
       </c>
-      <c r="L12" s="18">
-        <v>1</v>
-      </c>
-      <c r="M12" s="18">
+      <c r="L12" s="17">
+        <v>1</v>
+      </c>
+      <c r="M12" s="17">
         <v>1</v>
       </c>
       <c r="N12" s="2">
@@ -2282,20 +2285,78 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13" ht="16.5" spans="1:19">
+      <c r="A13" s="3">
+        <v>102100</v>
+      </c>
+      <c r="B13" s="2">
+        <v>102100001</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="3">
+        <v>3</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="13">
+        <v>1</v>
+      </c>
+      <c r="N13" s="11">
+        <v>20</v>
+      </c>
+      <c r="O13" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="P13" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>2</v>
+      </c>
+      <c r="R13" s="11">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="S13" s="3">
+        <v>1</v>
+      </c>
+    </row>
     <row r="19" spans="8:10">
-      <c r="J19" s="19"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" ht="16.5" spans="8:10">
-      <c r="H20" s="20"/>
+      <c r="H20" s="19"/>
     </row>
     <row r="21" ht="16.5" spans="8:10">
-      <c r="H21" s="20"/>
+      <c r="H21" s="19"/>
     </row>
     <row r="22" ht="16.5" spans="8:10">
-      <c r="H22" s="20"/>
+      <c r="H22" s="19"/>
     </row>
     <row r="23" ht="16.5" spans="8:10">
-      <c r="H23" s="20"/>
+      <c r="H23" s="19"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H23">

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
   <si>
     <t>游戏ID</t>
   </si>
@@ -483,6 +483,12 @@
   </si>
   <si>
     <t>102100101|102100102|102100103|102100104</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>101800101|101800102|101800103|101800104</t>
   </si>
 </sst>
 </file>
@@ -693,25 +699,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -724,6 +718,18 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1857,14 +1863,14 @@
         <v>1</v>
       </c>
       <c r="P5" s="11">
-        <f t="shared" ref="P5:P13" si="0">N5*M5*L5*O5</f>
+        <f t="shared" ref="P5:P14" si="0">N5*M5*L5*O5</f>
         <v>100</v>
       </c>
       <c r="Q5" s="11">
         <v>5</v>
       </c>
       <c r="R5" s="11">
-        <f t="shared" ref="R5:R13" si="1">P5*Q5/N5/M5</f>
+        <f t="shared" ref="R5:R14" si="1">P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
       <c r="S5" s="14">
@@ -2340,6 +2346,64 @@
         <v>0.1</v>
       </c>
       <c r="S13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:19">
+      <c r="A14" s="3">
+        <v>101800</v>
+      </c>
+      <c r="B14" s="3">
+        <v>101800001</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="3">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="13">
+        <v>1</v>
+      </c>
+      <c r="N14" s="11">
+        <v>20</v>
+      </c>
+      <c r="O14" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="P14" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>2</v>
+      </c>
+      <c r="R14" s="11">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="S14" s="3">
         <v>1</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -699,6 +699,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -706,6 +712,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -717,20 +729,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <strike/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2216,18 +2216,18 @@
         <v>20</v>
       </c>
       <c r="O11" s="11">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="P11" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q11" s="11">
         <v>2</v>
       </c>
       <c r="R11" s="11">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="S11" s="14">
         <v>1</v>
@@ -2332,18 +2332,18 @@
         <v>20</v>
       </c>
       <c r="O13" s="11">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="P13" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q13" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" s="11">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="S13" s="3">
         <v>1</v>
@@ -2353,7 +2353,7 @@
       <c r="A14" s="3">
         <v>101800</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>101800001</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -2368,7 +2368,7 @@
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="11" t="s">
         <v>31</v>
       </c>
       <c r="H14" s="11" t="s">
@@ -2390,18 +2390,18 @@
         <v>20</v>
       </c>
       <c r="O14" s="11">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="P14" s="11">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>N14*M14*L14*O14</f>
+        <v>20</v>
       </c>
       <c r="Q14" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" s="11">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="S14" s="3">
         <v>1</v>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
   <si>
     <t>游戏ID</t>
   </si>
@@ -489,6 +489,12 @@
   </si>
   <si>
     <t>101800101|101800102|101800103|101800104</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>102500101|102500102|102500103|102500104</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -716,8 +722,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -729,8 +735,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1863,14 +1869,14 @@
         <v>1</v>
       </c>
       <c r="P5" s="11">
-        <f t="shared" ref="P5:P14" si="0">N5*M5*L5*O5</f>
+        <f t="shared" ref="P5:P15" si="0">N5*M5*L5*O5</f>
         <v>100</v>
       </c>
       <c r="Q5" s="11">
         <v>5</v>
       </c>
       <c r="R5" s="11">
-        <f t="shared" ref="R5:R14" si="1">P5*Q5/N5/M5</f>
+        <f t="shared" ref="R5:R15" si="1">P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
       <c r="S5" s="14">
@@ -2291,23 +2297,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:19">
-      <c r="A13" s="3">
+    <row r="13" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A13" s="2">
         <v>102100</v>
       </c>
       <c r="B13" s="2">
         <v>102100001</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="15">
         <v>0</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="11">
         <v>1</v>
       </c>
       <c r="G13" s="11" t="s">
@@ -2316,19 +2322,19 @@
       <c r="H13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <v>3</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <v>5</v>
       </c>
-      <c r="L13" s="5">
-        <v>1</v>
-      </c>
-      <c r="M13" s="13">
-        <v>1</v>
-      </c>
-      <c r="N13" s="11">
+      <c r="L13" s="17">
+        <v>1</v>
+      </c>
+      <c r="M13" s="17">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2">
         <v>20</v>
       </c>
       <c r="O13" s="11">
@@ -2345,27 +2351,27 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S13" s="3">
+      <c r="S13" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:19">
-      <c r="A14" s="3">
+    <row r="14" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A14" s="2">
         <v>101800</v>
       </c>
       <c r="B14" s="2">
         <v>101800001</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="15">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="11">
         <v>0</v>
       </c>
       <c r="G14" s="11" t="s">
@@ -2374,26 +2380,26 @@
       <c r="H14" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <v>6</v>
       </c>
-      <c r="L14" s="5">
-        <v>1</v>
-      </c>
-      <c r="M14" s="13">
-        <v>1</v>
-      </c>
-      <c r="N14" s="11">
+      <c r="L14" s="17">
+        <v>1</v>
+      </c>
+      <c r="M14" s="17">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2">
         <v>20</v>
       </c>
       <c r="O14" s="11">
         <v>1</v>
       </c>
       <c r="P14" s="11">
-        <f>N14*M14*L14*O14</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="Q14" s="11">
@@ -2403,7 +2409,65 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A15" s="2">
+        <v>102500</v>
+      </c>
+      <c r="B15" s="2">
+        <v>102500001</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="11">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="2">
+        <v>3</v>
+      </c>
+      <c r="J15" s="2">
+        <v>5</v>
+      </c>
+      <c r="L15" s="17">
+        <v>1</v>
+      </c>
+      <c r="M15" s="17">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2">
+        <v>50</v>
+      </c>
+      <c r="O15" s="11">
+        <v>1</v>
+      </c>
+      <c r="P15" s="11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>1</v>
+      </c>
+      <c r="R15" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S15" s="14">
         <v>1</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="55">
   <si>
     <t>游戏ID</t>
   </si>
@@ -495,6 +495,12 @@
   </si>
   <si>
     <t>102500101|102500102|102500103|102500104</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>102300101|102300102|102300103|102300104</t>
   </si>
 </sst>
 </file>
@@ -705,7 +711,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -717,12 +723,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -735,7 +735,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <strike/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1869,14 +1875,14 @@
         <v>1</v>
       </c>
       <c r="P5" s="11">
-        <f t="shared" ref="P5:P15" si="0">N5*M5*L5*O5</f>
+        <f t="shared" ref="P5:P16" si="0">N5*M5*L5*O5</f>
         <v>100</v>
       </c>
       <c r="Q5" s="11">
         <v>5</v>
       </c>
       <c r="R5" s="11">
-        <f t="shared" ref="R5:R15" si="1">P5*Q5/N5/M5</f>
+        <f t="shared" ref="R5:R16" si="1">P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
       <c r="S5" s="14">
@@ -2468,6 +2474,64 @@
         <v>1</v>
       </c>
       <c r="S15" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A16" s="2">
+        <v>102300</v>
+      </c>
+      <c r="B16" s="2">
+        <v>102300001</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="15">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="11">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="2">
+        <v>4</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5</v>
+      </c>
+      <c r="L16" s="17">
+        <v>1</v>
+      </c>
+      <c r="M16" s="17">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2">
+        <v>20</v>
+      </c>
+      <c r="O16" s="11">
+        <v>1</v>
+      </c>
+      <c r="P16" s="11">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>1</v>
+      </c>
+      <c r="R16" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S16" s="14">
         <v>1</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
   <si>
     <t>游戏ID</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>102300101|102300102|102300103|102300104</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
   </si>
 </sst>
 </file>
@@ -711,18 +714,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -741,7 +744,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2535,19 +2538,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="8:10">
+    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A17" s="2">
+        <v>103400</v>
+      </c>
+      <c r="B17" s="2">
+        <v>103400001</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="2">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3</v>
+      </c>
+      <c r="L17" s="17">
+        <v>1</v>
+      </c>
+      <c r="M17" s="17">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2">
+        <v>5</v>
+      </c>
+      <c r="O17" s="11">
+        <v>1</v>
+      </c>
+      <c r="P17" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>1</v>
+      </c>
+      <c r="R17" s="11">
+        <v>1</v>
+      </c>
+      <c r="S17" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="J19" s="18"/>
     </row>
-    <row r="20" ht="16.5" spans="8:10">
+    <row r="20" ht="16.5" spans="1:19">
       <c r="H20" s="19"/>
     </row>
-    <row r="21" ht="16.5" spans="8:10">
+    <row r="21" ht="16.5" spans="1:19">
       <c r="H21" s="19"/>
     </row>
-    <row r="22" ht="16.5" spans="8:10">
+    <row r="22" ht="16.5" spans="1:19">
       <c r="H22" s="19"/>
     </row>
-    <row r="23" ht="16.5" spans="8:10">
+    <row r="23" ht="16.5" spans="1:19">
       <c r="H23" s="19"/>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
   <si>
     <t>游戏ID</t>
   </si>
@@ -501,6 +501,21 @@
   </si>
   <si>
     <t>102300101|102300102|102300103|102300104</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>103500101|103500102|103500103|103500104</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>103501101|103501102|103501103|103501104</t>
   </si>
 </sst>
 </file>
@@ -711,12 +726,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -724,6 +733,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -735,14 +750,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <strike/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1240,7 +1255,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1294,9 +1309,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2535,20 +2547,185 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="8:10">
-      <c r="J19" s="18"/>
+    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A17" s="2">
+        <v>103400</v>
+      </c>
+      <c r="B17" s="2">
+        <v>103400001</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="11">
+        <v>103400101</v>
+      </c>
+      <c r="I17" s="2">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3</v>
+      </c>
+      <c r="L17" s="17">
+        <v>1</v>
+      </c>
+      <c r="M17" s="17">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2">
+        <v>5</v>
+      </c>
+      <c r="O17" s="11">
+        <v>1</v>
+      </c>
+      <c r="P17" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>1</v>
+      </c>
+      <c r="R17" s="11">
+        <v>1</v>
+      </c>
+      <c r="S17" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" ht="16.5" spans="8:10">
-      <c r="H20" s="19"/>
+    <row r="18" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A18" s="2">
+        <v>103500</v>
+      </c>
+      <c r="B18" s="2">
+        <v>103500001</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="2">
+        <v>4</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3</v>
+      </c>
+      <c r="L18" s="17">
+        <v>1</v>
+      </c>
+      <c r="M18" s="17">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2">
+        <v>10</v>
+      </c>
+      <c r="O18" s="11">
+        <v>1</v>
+      </c>
+      <c r="P18" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>1</v>
+      </c>
+      <c r="R18" s="11">
+        <v>1</v>
+      </c>
+      <c r="S18" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" ht="16.5" spans="8:10">
-      <c r="H21" s="19"/>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A19" s="2">
+        <v>103501</v>
+      </c>
+      <c r="B19" s="2">
+        <v>103501001</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="11">
+        <v>0</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="2">
+        <v>4</v>
+      </c>
+      <c r="J19" s="2">
+        <v>3</v>
+      </c>
+      <c r="L19" s="17">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2">
+        <v>10</v>
+      </c>
+      <c r="O19" s="11">
+        <v>1</v>
+      </c>
+      <c r="P19" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>1</v>
+      </c>
+      <c r="R19" s="11">
+        <v>1</v>
+      </c>
+      <c r="S19" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" ht="16.5" spans="8:10">
-      <c r="H22" s="19"/>
+    <row r="20" ht="16.5" spans="1:19">
+      <c r="H20" s="18"/>
     </row>
-    <row r="23" ht="16.5" spans="8:10">
-      <c r="H23" s="19"/>
+    <row r="21" ht="16.5" spans="1:19">
+      <c r="H21" s="18"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:19">
+      <c r="H22" s="18"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:19">
+      <c r="H23" s="18"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H23">

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
   <si>
     <t>游戏ID</t>
   </si>
@@ -504,6 +504,18 @@
   </si>
   <si>
     <t>神马飞扬</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>103500101|103500102|103500103|103500104</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>103501101|103501102|103501103|103501104</t>
   </si>
 </sst>
 </file>
@@ -714,19 +726,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -738,14 +750,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <strike/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1243,7 +1255,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1297,9 +1309,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2560,7 +2569,9 @@
       <c r="G17" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="11"/>
+      <c r="H17" s="11">
+        <v>103400101</v>
+      </c>
       <c r="I17" s="2">
         <v>3</v>
       </c>
@@ -2592,20 +2603,129 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
-      <c r="J19" s="18"/>
+    <row r="18" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A18" s="2">
+        <v>103500</v>
+      </c>
+      <c r="B18" s="2">
+        <v>103500001</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="2">
+        <v>4</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3</v>
+      </c>
+      <c r="L18" s="17">
+        <v>1</v>
+      </c>
+      <c r="M18" s="17">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2">
+        <v>10</v>
+      </c>
+      <c r="O18" s="11">
+        <v>1</v>
+      </c>
+      <c r="P18" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>1</v>
+      </c>
+      <c r="R18" s="11">
+        <v>1</v>
+      </c>
+      <c r="S18" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A19" s="2">
+        <v>103501</v>
+      </c>
+      <c r="B19" s="2">
+        <v>103501001</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="11">
+        <v>0</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="2">
+        <v>4</v>
+      </c>
+      <c r="J19" s="2">
+        <v>3</v>
+      </c>
+      <c r="L19" s="17">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2">
+        <v>10</v>
+      </c>
+      <c r="O19" s="11">
+        <v>1</v>
+      </c>
+      <c r="P19" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>1</v>
+      </c>
+      <c r="R19" s="11">
+        <v>1</v>
+      </c>
+      <c r="S19" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" ht="16.5" spans="1:19">
-      <c r="H20" s="19"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" ht="16.5" spans="1:19">
-      <c r="H21" s="19"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" ht="16.5" spans="1:19">
-      <c r="H22" s="19"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" ht="16.5" spans="1:19">
-      <c r="H23" s="19"/>
+      <c r="H23" s="18"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H23">

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -711,12 +711,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -724,6 +718,18 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -737,12 +743,6 @@
     <font>
       <strike/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1872,18 +1872,18 @@
         <v>50</v>
       </c>
       <c r="O5" s="11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="P5" s="11">
         <f t="shared" ref="P5:P16" si="0">N5*M5*L5*O5</f>
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="Q5" s="11">
         <v>5</v>
       </c>
       <c r="R5" s="11">
         <f t="shared" ref="R5:R16" si="1">P5*Q5/N5/M5</f>
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="S5" s="14">
         <v>1</v>
@@ -2169,18 +2169,18 @@
         <v>50</v>
       </c>
       <c r="O10" s="11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P10" s="11">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Q10" s="11">
         <v>5</v>
       </c>
       <c r="R10" s="11">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="S10" s="14">
         <v>1</v>
@@ -2286,18 +2286,18 @@
         <v>25</v>
       </c>
       <c r="O12" s="11">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="P12" s="11">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Q12" s="11">
         <v>1</v>
       </c>
       <c r="R12" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="S12" s="14">
         <v>1</v>
@@ -2402,18 +2402,18 @@
         <v>20</v>
       </c>
       <c r="O14" s="11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="P14" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Q14" s="11">
         <v>1</v>
       </c>
       <c r="R14" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="S14" s="14">
         <v>1</v>
@@ -2460,18 +2460,18 @@
         <v>50</v>
       </c>
       <c r="O15" s="11">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="Q15" s="11">
         <v>1</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="S15" s="14">
         <v>1</v>
@@ -2518,18 +2518,18 @@
         <v>20</v>
       </c>
       <c r="O16" s="11">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="P16" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>50000</v>
       </c>
       <c r="Q16" s="11">
         <v>1</v>
       </c>
       <c r="R16" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="S16" s="14">
         <v>1</v>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
   <si>
     <t>游戏ID</t>
   </si>
@@ -501,6 +501,21 @@
   </si>
   <si>
     <t>102300101|102300102|102300103|102300104</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>103500101|103500102|103500103|103500104</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>103501101|103501102|103501103|103501104</t>
   </si>
 </sst>
 </file>
@@ -728,13 +743,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1240,7 +1255,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1294,9 +1309,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1872,18 +1884,18 @@
         <v>50</v>
       </c>
       <c r="O5" s="11">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P5" s="11">
         <f t="shared" ref="P5:P16" si="0">N5*M5*L5*O5</f>
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="Q5" s="11">
         <v>5</v>
       </c>
       <c r="R5" s="11">
         <f t="shared" ref="R5:R16" si="1">P5*Q5/N5/M5</f>
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="S5" s="14">
         <v>1</v>
@@ -2169,18 +2181,18 @@
         <v>50</v>
       </c>
       <c r="O10" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P10" s="11">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="11">
         <v>5</v>
       </c>
       <c r="R10" s="11">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="S10" s="14">
         <v>1</v>
@@ -2286,18 +2298,18 @@
         <v>25</v>
       </c>
       <c r="O12" s="11">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="P12" s="11">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Q12" s="11">
         <v>1</v>
       </c>
       <c r="R12" s="11">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="S12" s="14">
         <v>1</v>
@@ -2402,18 +2414,18 @@
         <v>20</v>
       </c>
       <c r="O14" s="11">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P14" s="11">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Q14" s="11">
         <v>1</v>
       </c>
       <c r="R14" s="11">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="S14" s="14">
         <v>1</v>
@@ -2460,18 +2472,18 @@
         <v>50</v>
       </c>
       <c r="O15" s="11">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="0"/>
-        <v>50000</v>
+        <v>50</v>
       </c>
       <c r="Q15" s="11">
         <v>1</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="S15" s="14">
         <v>1</v>
@@ -2518,37 +2530,202 @@
         <v>20</v>
       </c>
       <c r="O16" s="11">
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="P16" s="11">
         <f t="shared" si="0"/>
-        <v>50000</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="11">
         <v>1</v>
       </c>
       <c r="R16" s="11">
         <f t="shared" si="1"/>
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="S16" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="8:10">
-      <c r="J19" s="18"/>
+    <row r="17" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A17" s="2">
+        <v>103400</v>
+      </c>
+      <c r="B17" s="2">
+        <v>103400001</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="11">
+        <v>103400101</v>
+      </c>
+      <c r="I17" s="2">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3</v>
+      </c>
+      <c r="L17" s="17">
+        <v>1</v>
+      </c>
+      <c r="M17" s="17">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2">
+        <v>5</v>
+      </c>
+      <c r="O17" s="11">
+        <v>1</v>
+      </c>
+      <c r="P17" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>1</v>
+      </c>
+      <c r="R17" s="11">
+        <v>1</v>
+      </c>
+      <c r="S17" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" ht="16.5" spans="8:10">
-      <c r="H20" s="19"/>
+    <row r="18" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A18" s="2">
+        <v>103500</v>
+      </c>
+      <c r="B18" s="2">
+        <v>103500001</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="2">
+        <v>4</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3</v>
+      </c>
+      <c r="L18" s="17">
+        <v>1</v>
+      </c>
+      <c r="M18" s="17">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2">
+        <v>10</v>
+      </c>
+      <c r="O18" s="11">
+        <v>1</v>
+      </c>
+      <c r="P18" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>1</v>
+      </c>
+      <c r="R18" s="11">
+        <v>1</v>
+      </c>
+      <c r="S18" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" ht="16.5" spans="8:10">
-      <c r="H21" s="19"/>
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A19" s="2">
+        <v>103501</v>
+      </c>
+      <c r="B19" s="2">
+        <v>103501001</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="11">
+        <v>0</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="2">
+        <v>4</v>
+      </c>
+      <c r="J19" s="2">
+        <v>3</v>
+      </c>
+      <c r="L19" s="17">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2">
+        <v>10</v>
+      </c>
+      <c r="O19" s="11">
+        <v>1</v>
+      </c>
+      <c r="P19" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>1</v>
+      </c>
+      <c r="R19" s="11">
+        <v>1</v>
+      </c>
+      <c r="S19" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" ht="16.5" spans="8:10">
-      <c r="H22" s="19"/>
+    <row r="20" ht="16.5" spans="1:19">
+      <c r="H20" s="18"/>
     </row>
-    <row r="23" ht="16.5" spans="8:10">
-      <c r="H23" s="19"/>
+    <row r="21" ht="16.5" spans="1:19">
+      <c r="H21" s="18"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:19">
+      <c r="H22" s="18"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:19">
+      <c r="H23" s="18"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H23">

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
   <si>
     <t>游戏ID</t>
   </si>
@@ -516,6 +516,9 @@
   </si>
   <si>
     <t>103501101|103501102|103501103|103501104</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
   </si>
 </sst>
 </file>
@@ -726,6 +729,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -737,8 +746,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -752,12 +761,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2715,8 +2718,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:19">
-      <c r="H20" s="18"/>
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A20" s="2">
+        <v>103600</v>
+      </c>
+      <c r="B20" s="2">
+        <v>103600001</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="11">
+        <v>0</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="11">
+        <v>103600101</v>
+      </c>
+      <c r="I20" s="2">
+        <v>3</v>
+      </c>
+      <c r="J20" s="2">
+        <v>3</v>
+      </c>
+      <c r="L20" s="17">
+        <v>1</v>
+      </c>
+      <c r="M20" s="17">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2">
+        <v>5</v>
+      </c>
+      <c r="O20" s="11">
+        <v>1</v>
+      </c>
+      <c r="P20" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>1</v>
+      </c>
+      <c r="R20" s="11">
+        <v>1</v>
+      </c>
+      <c r="S20" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" ht="16.5" spans="1:19">
       <c r="H21" s="18"/>
@@ -2731,7 +2787,7 @@
   <conditionalFormatting sqref="H23">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20:H22">
+  <conditionalFormatting sqref="H21:H22">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t>游戏ID</t>
   </si>
@@ -519,6 +519,21 @@
   </si>
   <si>
     <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>王牌DJ</t>
+  </si>
+  <si>
+    <t>102800101|102800102|102800103|102800104</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>102000101|102000102|102000103|102000104</t>
   </si>
 </sst>
 </file>
@@ -531,7 +546,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,13 +593,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -729,24 +737,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -760,10 +751,27 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -971,7 +979,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -991,21 +999,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1127,138 +1120,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1312,9 +1305,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1369,18 +1359,6 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1890,14 +1868,14 @@
         <v>1</v>
       </c>
       <c r="P5" s="11">
-        <f t="shared" ref="P5:P16" si="0">N5*M5*L5*O5</f>
+        <f>N5*M5*L5*O5</f>
         <v>100</v>
       </c>
       <c r="Q5" s="11">
         <v>5</v>
       </c>
       <c r="R5" s="11">
-        <f t="shared" ref="R5:R16" si="1">P5*Q5/N5/M5</f>
+        <f t="shared" ref="R5:R16" si="0">P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
       <c r="S5" s="14">
@@ -1949,14 +1927,14 @@
         <v>1</v>
       </c>
       <c r="P6" s="11">
+        <f t="shared" ref="P6:P23" si="1">N6*M6*L6*O6</f>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>1</v>
+      </c>
+      <c r="R6" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>1</v>
-      </c>
-      <c r="R6" s="11">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S6" s="14">
@@ -2008,14 +1986,14 @@
         <v>0.05</v>
       </c>
       <c r="P7" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q7" s="11">
         <v>2</v>
       </c>
       <c r="R7" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="S7" s="14">
@@ -2067,14 +2045,14 @@
         <v>1</v>
       </c>
       <c r="P8" s="11">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>1</v>
+      </c>
+      <c r="R8" s="11">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>1</v>
-      </c>
-      <c r="R8" s="11">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S8" s="14">
@@ -2126,14 +2104,14 @@
         <v>0.05</v>
       </c>
       <c r="P9" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="Q9" s="11">
         <v>6</v>
       </c>
       <c r="R9" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="S9" s="14">
@@ -2187,14 +2165,14 @@
         <v>1</v>
       </c>
       <c r="P10" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="Q10" s="11">
         <v>5</v>
       </c>
       <c r="R10" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="S10" s="14">
@@ -2246,14 +2224,14 @@
         <v>1</v>
       </c>
       <c r="P11" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="Q11" s="11">
         <v>2</v>
       </c>
       <c r="R11" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="S11" s="14">
@@ -2304,14 +2282,14 @@
         <v>1</v>
       </c>
       <c r="P12" s="11">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>1</v>
+      </c>
+      <c r="R12" s="11">
         <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>1</v>
-      </c>
-      <c r="R12" s="11">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S12" s="14">
@@ -2362,14 +2340,14 @@
         <v>1</v>
       </c>
       <c r="P13" s="11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>1</v>
+      </c>
+      <c r="R13" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>1</v>
-      </c>
-      <c r="R13" s="11">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S13" s="14">
@@ -2420,14 +2398,14 @@
         <v>1</v>
       </c>
       <c r="P14" s="11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>1</v>
+      </c>
+      <c r="R14" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>1</v>
-      </c>
-      <c r="R14" s="11">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S14" s="14">
@@ -2478,14 +2456,14 @@
         <v>1</v>
       </c>
       <c r="P15" s="11">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>1</v>
+      </c>
+      <c r="R15" s="11">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>1</v>
-      </c>
-      <c r="R15" s="11">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S15" s="14">
@@ -2536,14 +2514,14 @@
         <v>1</v>
       </c>
       <c r="P16" s="11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>1</v>
+      </c>
+      <c r="R16" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="Q16" s="11">
-        <v>1</v>
-      </c>
-      <c r="R16" s="11">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S16" s="14">
@@ -2555,7 +2533,7 @@
         <v>103400</v>
       </c>
       <c r="B17" s="2">
-        <v>103400001</v>
+        <v>103000001</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>55</v>
@@ -2573,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="H17" s="11">
-        <v>103400101</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
         <v>3</v>
@@ -2594,6 +2572,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="11">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="Q17" s="11">
@@ -2611,7 +2590,7 @@
         <v>103500</v>
       </c>
       <c r="B18" s="2">
-        <v>103500001</v>
+        <v>102900001</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>56</v>
@@ -2650,6 +2629,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="11">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q18" s="11">
@@ -2706,6 +2686,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="11">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="Q19" s="11">
@@ -2762,6 +2743,7 @@
         <v>1</v>
       </c>
       <c r="P20" s="11">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="Q20" s="11">
@@ -2774,22 +2756,178 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:19">
-      <c r="H21" s="18"/>
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A21" s="2">
+        <v>102800</v>
+      </c>
+      <c r="B21" s="2">
+        <v>102800001</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="11">
+        <v>1</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="2">
+        <v>5</v>
+      </c>
+      <c r="J21" s="2">
+        <v>6</v>
+      </c>
+      <c r="L21" s="17">
+        <v>1</v>
+      </c>
+      <c r="M21" s="17">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2">
+        <v>20</v>
+      </c>
+      <c r="O21" s="11">
+        <v>1</v>
+      </c>
+      <c r="P21" s="11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>1</v>
+      </c>
+      <c r="R21" s="11">
+        <v>1</v>
+      </c>
+      <c r="S21" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" ht="16.5" spans="1:19">
-      <c r="H22" s="18"/>
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A22" s="2">
+        <v>103401</v>
+      </c>
+      <c r="B22" s="2">
+        <v>103400001</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="11">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>3</v>
+      </c>
+      <c r="J22" s="2">
+        <v>3</v>
+      </c>
+      <c r="L22" s="17">
+        <v>1</v>
+      </c>
+      <c r="M22" s="17">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2">
+        <v>5</v>
+      </c>
+      <c r="O22" s="11">
+        <v>1</v>
+      </c>
+      <c r="P22" s="11">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>1</v>
+      </c>
+      <c r="R22" s="11">
+        <v>1</v>
+      </c>
+      <c r="S22" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" ht="16.5" spans="1:19">
-      <c r="H23" s="18"/>
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A23" s="2">
+        <v>102000</v>
+      </c>
+      <c r="B23" s="2">
+        <v>102200001</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="11">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5</v>
+      </c>
+      <c r="J23" s="2">
+        <v>5</v>
+      </c>
+      <c r="L23" s="17">
+        <v>1</v>
+      </c>
+      <c r="M23" s="17">
+        <v>1</v>
+      </c>
+      <c r="N23" s="2">
+        <v>15</v>
+      </c>
+      <c r="O23" s="11">
+        <v>1</v>
+      </c>
+      <c r="P23" s="11">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>1</v>
+      </c>
+      <c r="R23" s="11">
+        <v>1</v>
+      </c>
+      <c r="S23" s="14">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H22">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
   <si>
     <t>游戏ID</t>
   </si>
@@ -534,6 +534,12 @@
   </si>
   <si>
     <t>102000101|102000102|102000103|102000104</t>
+  </si>
+  <si>
+    <t>恶魔之子</t>
+  </si>
+  <si>
+    <t>103800101|103800102|103800103|103800104</t>
   </si>
 </sst>
 </file>
@@ -743,6 +749,23 @@
       <charset val="134"/>
     </font>
     <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -750,25 +773,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1646,7 +1652,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2927,6 +2933,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="24" ht="16.5" spans="1:19">
+      <c r="A24" s="3">
+        <v>103800</v>
+      </c>
+      <c r="B24" s="3">
+        <v>103800001</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>5</v>
+      </c>
+      <c r="L24" s="5">
+        <v>1</v>
+      </c>
+      <c r="M24" s="5">
+        <v>1</v>
+      </c>
+      <c r="N24" s="3">
+        <v>40</v>
+      </c>
+      <c r="O24" s="3">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1</v>
+      </c>
+      <c r="S24" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
   <si>
     <t>游戏ID</t>
   </si>
@@ -540,6 +540,15 @@
   </si>
   <si>
     <t>103800101|103800102|103800103|103800104</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>102700101|102700102|102700103|102700104</t>
+  </si>
+  <si>
+    <t>10倍金牛</t>
   </si>
 </sst>
 </file>
@@ -743,19 +752,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
+      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -766,9 +776,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <strike/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1652,7 +1661,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2557,7 +2566,7 @@
         <v>31</v>
       </c>
       <c r="H17" s="11">
-        <v>0</v>
+        <v>103400101</v>
       </c>
       <c r="I17" s="2">
         <v>3</v>
@@ -2824,7 +2833,7 @@
         <v>103401</v>
       </c>
       <c r="B22" s="2">
-        <v>103400001</v>
+        <v>103401001</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>63</v>
@@ -2842,7 +2851,7 @@
         <v>31</v>
       </c>
       <c r="H22" s="11">
-        <v>0</v>
+        <v>103401101</v>
       </c>
       <c r="I22" s="2">
         <v>3</v>
@@ -2986,6 +2995,118 @@
         <v>1</v>
       </c>
       <c r="S24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:19">
+      <c r="A25" s="3">
+        <v>102700</v>
+      </c>
+      <c r="B25" s="3">
+        <v>102700001</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="3">
+        <v>3</v>
+      </c>
+      <c r="J25" s="3">
+        <v>5</v>
+      </c>
+      <c r="L25" s="5">
+        <v>1</v>
+      </c>
+      <c r="M25" s="5">
+        <v>1</v>
+      </c>
+      <c r="N25" s="3">
+        <v>20</v>
+      </c>
+      <c r="O25" s="3">
+        <v>1</v>
+      </c>
+      <c r="P25" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3">
+        <v>1</v>
+      </c>
+      <c r="S25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:19">
+      <c r="A26" s="3">
+        <v>103700</v>
+      </c>
+      <c r="B26" s="3">
+        <v>103700001</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3</v>
+      </c>
+      <c r="L26" s="5">
+        <v>1</v>
+      </c>
+      <c r="M26" s="5">
+        <v>1</v>
+      </c>
+      <c r="N26" s="3">
+        <v>10</v>
+      </c>
+      <c r="O26" s="3">
+        <v>1</v>
+      </c>
+      <c r="P26" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3">
+        <v>1</v>
+      </c>
+      <c r="S26" s="3">
         <v>1</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="73">
   <si>
     <t>游戏ID</t>
   </si>
@@ -549,6 +549,12 @@
   </si>
   <si>
     <t>10倍金牛</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <t>103100101|103100102|103100103|103100104</t>
   </si>
 </sst>
 </file>
@@ -752,12 +758,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -776,14 +782,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1661,7 +1667,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -3077,7 +3083,7 @@
         <v>31</v>
       </c>
       <c r="H26" s="11">
-        <v>0</v>
+        <v>103700101</v>
       </c>
       <c r="I26" s="3">
         <v>4</v>
@@ -3107,6 +3113,62 @@
         <v>1</v>
       </c>
       <c r="S26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:19">
+      <c r="A27" s="3">
+        <v>103100</v>
+      </c>
+      <c r="B27" s="3">
+        <v>103100001</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I27" s="3">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
+        <v>5</v>
+      </c>
+      <c r="L27" s="5">
+        <v>1</v>
+      </c>
+      <c r="M27" s="5">
+        <v>1</v>
+      </c>
+      <c r="N27" s="3">
+        <v>25</v>
+      </c>
+      <c r="O27" s="3">
+        <v>1</v>
+      </c>
+      <c r="P27" s="3">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1</v>
+      </c>
+      <c r="S27" s="3">
         <v>1</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="77">
   <si>
     <t>游戏ID</t>
   </si>
@@ -555,6 +555,18 @@
   </si>
   <si>
     <t>103100101|103100102|103100103|103100104</t>
+  </si>
+  <si>
+    <t>潘金莲</t>
+  </si>
+  <si>
+    <t>104000101|104000102|104000103|104000104</t>
+  </si>
+  <si>
+    <t>愤怒的小鸡</t>
+  </si>
+  <si>
+    <t>103900101|103900102|103900103|103900104</t>
   </si>
 </sst>
 </file>
@@ -758,8 +770,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -772,24 +802,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1667,7 +1679,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -3172,6 +3184,118 @@
         <v>1</v>
       </c>
     </row>
+    <row r="28" ht="16.5" spans="1:19">
+      <c r="A28" s="3">
+        <v>104000</v>
+      </c>
+      <c r="B28" s="3">
+        <v>104000001</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="3">
+        <v>3</v>
+      </c>
+      <c r="J28" s="3">
+        <v>5</v>
+      </c>
+      <c r="L28" s="5">
+        <v>1</v>
+      </c>
+      <c r="M28" s="5">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3">
+        <v>40</v>
+      </c>
+      <c r="O28" s="3">
+        <v>1</v>
+      </c>
+      <c r="P28" s="3">
+        <v>40</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3">
+        <v>1</v>
+      </c>
+      <c r="S28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:19">
+      <c r="A29" s="3">
+        <v>103900</v>
+      </c>
+      <c r="B29" s="3">
+        <v>103900001</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="3">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
+        <v>5</v>
+      </c>
+      <c r="L29" s="5">
+        <v>1</v>
+      </c>
+      <c r="M29" s="5">
+        <v>1</v>
+      </c>
+      <c r="N29" s="3">
+        <v>25</v>
+      </c>
+      <c r="O29" s="3">
+        <v>1</v>
+      </c>
+      <c r="P29" s="3">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1</v>
+      </c>
+      <c r="S29" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
   <si>
     <t>游戏ID</t>
   </si>
@@ -567,6 +567,12 @@
   </si>
   <si>
     <t>103900101|103900102|103900103|103900104</t>
+  </si>
+  <si>
+    <t>热血足球</t>
+  </si>
+  <si>
+    <t>101600101|106100102|101600103|101600104</t>
   </si>
 </sst>
 </file>
@@ -770,13 +776,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -788,19 +793,20 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1679,7 +1685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -3296,6 +3302,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="30" ht="16.5" spans="1:19">
+      <c r="A30" s="3">
+        <v>101600</v>
+      </c>
+      <c r="B30" s="3">
+        <v>101600001</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="3">
+        <v>6</v>
+      </c>
+      <c r="J30" s="3">
+        <v>6</v>
+      </c>
+      <c r="L30" s="5">
+        <v>1</v>
+      </c>
+      <c r="M30" s="5">
+        <v>1</v>
+      </c>
+      <c r="N30" s="3">
+        <v>20</v>
+      </c>
+      <c r="O30" s="3">
+        <v>1</v>
+      </c>
+      <c r="P30" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>1</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1</v>
+      </c>
+      <c r="S30" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="81">
   <si>
     <t>游戏ID</t>
   </si>
@@ -572,7 +572,13 @@
     <t>热血足球</t>
   </si>
   <si>
-    <t>101600101|106100102|101600103|101600104</t>
+    <t>101600101|101600102|101600103|101600104</t>
+  </si>
+  <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>101500101|101500102|101500103|101500104</t>
   </si>
 </sst>
 </file>
@@ -776,18 +782,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -801,7 +802,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1685,7 +1691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -3358,6 +3364,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="31" ht="16.5" spans="1:19">
+      <c r="A31" s="3">
+        <v>101500</v>
+      </c>
+      <c r="B31" s="3">
+        <v>101500001</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3</v>
+      </c>
+      <c r="J31" s="3">
+        <v>5</v>
+      </c>
+      <c r="L31" s="5">
+        <v>1</v>
+      </c>
+      <c r="M31" s="5">
+        <v>1</v>
+      </c>
+      <c r="N31" s="3">
+        <v>20</v>
+      </c>
+      <c r="O31" s="3">
+        <v>1</v>
+      </c>
+      <c r="P31" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>1</v>
+      </c>
+      <c r="R31" s="3">
+        <v>1</v>
+      </c>
+      <c r="S31" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="13665" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="87">
   <si>
     <t>游戏ID</t>
   </si>
@@ -585,6 +585,18 @@
   </si>
   <si>
     <t>102600101|102600102|102600103|102600104</t>
+  </si>
+  <si>
+    <t>澳门壕梦</t>
+  </si>
+  <si>
+    <t>105000101|105000102|105000103|105000104</t>
+  </si>
+  <si>
+    <t>糖果派对</t>
+  </si>
+  <si>
+    <t>105100101|105100102|105100103|105100104</t>
   </si>
 </sst>
 </file>
@@ -807,9 +819,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <strike/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -819,14 +830,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1315,7 +1327,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1374,9 +1386,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1725,7 +1734,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -3020,10 +3029,10 @@
       <c r="B24" s="4">
         <v>103800001</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="20">
         <v>1</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -3045,10 +3054,10 @@
         <v>5</v>
       </c>
       <c r="K24" s="4"/>
-      <c r="L24" s="22">
-        <v>1</v>
-      </c>
-      <c r="M24" s="22">
+      <c r="L24" s="21">
+        <v>1</v>
+      </c>
+      <c r="M24" s="21">
         <v>1</v>
       </c>
       <c r="N24" s="4">
@@ -3079,10 +3088,10 @@
       <c r="B25" s="4">
         <v>102700001</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="20">
         <v>0</v>
       </c>
       <c r="E25" s="17" t="s">
@@ -3104,10 +3113,10 @@
         <v>5</v>
       </c>
       <c r="K25" s="4"/>
-      <c r="L25" s="22">
-        <v>1</v>
-      </c>
-      <c r="M25" s="22">
+      <c r="L25" s="21">
+        <v>1</v>
+      </c>
+      <c r="M25" s="21">
         <v>1</v>
       </c>
       <c r="N25" s="4">
@@ -3138,10 +3147,10 @@
       <c r="B26" s="4">
         <v>103700001</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="20">
         <v>1</v>
       </c>
       <c r="E26" s="17" t="s">
@@ -3163,10 +3172,10 @@
         <v>3</v>
       </c>
       <c r="K26" s="4"/>
-      <c r="L26" s="22">
-        <v>1</v>
-      </c>
-      <c r="M26" s="22">
+      <c r="L26" s="21">
+        <v>1</v>
+      </c>
+      <c r="M26" s="21">
         <v>1</v>
       </c>
       <c r="N26" s="4">
@@ -3197,10 +3206,10 @@
       <c r="B27" s="4">
         <v>103100001</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="20">
         <v>1</v>
       </c>
       <c r="E27" s="17" t="s">
@@ -3222,10 +3231,10 @@
         <v>5</v>
       </c>
       <c r="K27" s="4"/>
-      <c r="L27" s="22">
-        <v>1</v>
-      </c>
-      <c r="M27" s="22">
+      <c r="L27" s="21">
+        <v>1</v>
+      </c>
+      <c r="M27" s="21">
         <v>1</v>
       </c>
       <c r="N27" s="4">
@@ -3256,10 +3265,10 @@
       <c r="B28" s="4">
         <v>104000001</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="20">
         <v>1</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -3281,10 +3290,10 @@
         <v>5</v>
       </c>
       <c r="K28" s="4"/>
-      <c r="L28" s="22">
-        <v>1</v>
-      </c>
-      <c r="M28" s="22">
+      <c r="L28" s="21">
+        <v>1</v>
+      </c>
+      <c r="M28" s="21">
         <v>1</v>
       </c>
       <c r="N28" s="4">
@@ -3315,10 +3324,10 @@
       <c r="B29" s="4">
         <v>103900001</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="20">
         <v>1</v>
       </c>
       <c r="E29" s="17" t="s">
@@ -3340,10 +3349,10 @@
         <v>5</v>
       </c>
       <c r="K29" s="4"/>
-      <c r="L29" s="22">
-        <v>1</v>
-      </c>
-      <c r="M29" s="22">
+      <c r="L29" s="21">
+        <v>1</v>
+      </c>
+      <c r="M29" s="21">
         <v>1</v>
       </c>
       <c r="N29" s="4">
@@ -3374,10 +3383,10 @@
       <c r="B30" s="4">
         <v>101600001</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="20">
         <v>0</v>
       </c>
       <c r="E30" s="17" t="s">
@@ -3399,10 +3408,10 @@
         <v>6</v>
       </c>
       <c r="K30" s="4"/>
-      <c r="L30" s="22">
-        <v>1</v>
-      </c>
-      <c r="M30" s="22">
+      <c r="L30" s="21">
+        <v>1</v>
+      </c>
+      <c r="M30" s="21">
         <v>1</v>
       </c>
       <c r="N30" s="4">
@@ -3433,10 +3442,10 @@
       <c r="B31" s="4">
         <v>101500001</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="20">
         <v>0</v>
       </c>
       <c r="E31" s="17" t="s">
@@ -3458,10 +3467,10 @@
         <v>5</v>
       </c>
       <c r="K31" s="4"/>
-      <c r="L31" s="22">
-        <v>1</v>
-      </c>
-      <c r="M31" s="22">
+      <c r="L31" s="21">
+        <v>1</v>
+      </c>
+      <c r="M31" s="21">
         <v>1</v>
       </c>
       <c r="N31" s="4">
@@ -3492,10 +3501,10 @@
       <c r="B32" s="4">
         <v>102600001</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="20">
         <v>0</v>
       </c>
       <c r="E32" s="17" t="s">
@@ -3517,10 +3526,10 @@
         <v>5</v>
       </c>
       <c r="K32" s="4"/>
-      <c r="L32" s="22">
-        <v>1</v>
-      </c>
-      <c r="M32" s="22">
+      <c r="L32" s="21">
+        <v>1</v>
+      </c>
+      <c r="M32" s="21">
         <v>1</v>
       </c>
       <c r="N32" s="4">
@@ -3541,6 +3550,120 @@
         <v>1</v>
       </c>
       <c r="S32" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A33" s="4">
+        <v>105000</v>
+      </c>
+      <c r="B33" s="4">
+        <v>105000001</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" s="4">
+        <v>5</v>
+      </c>
+      <c r="J33" s="4">
+        <v>6</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="21">
+        <v>1</v>
+      </c>
+      <c r="M33" s="21">
+        <v>1</v>
+      </c>
+      <c r="N33" s="4">
+        <v>20</v>
+      </c>
+      <c r="O33" s="4">
+        <v>1</v>
+      </c>
+      <c r="P33" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>1</v>
+      </c>
+      <c r="R33" s="13">
+        <v>1</v>
+      </c>
+      <c r="S33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A34" s="4">
+        <v>105100</v>
+      </c>
+      <c r="B34" s="4">
+        <v>105100001</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I34" s="5">
+        <v>6</v>
+      </c>
+      <c r="J34" s="5">
+        <v>6</v>
+      </c>
+      <c r="K34" s="5"/>
+      <c r="L34" s="21">
+        <v>1</v>
+      </c>
+      <c r="M34" s="21">
+        <v>1</v>
+      </c>
+      <c r="N34" s="5">
+        <v>10</v>
+      </c>
+      <c r="O34" s="4">
+        <v>1</v>
+      </c>
+      <c r="P34" s="13">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>1</v>
+      </c>
+      <c r="R34" s="13">
+        <v>1</v>
+      </c>
+      <c r="S34" s="4">
         <v>1</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13665" windowHeight="12315"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -815,11 +815,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -830,8 +831,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -843,8 +843,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3523,7 +3523,7 @@
         <v>6</v>
       </c>
       <c r="J32" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="21">

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="13665" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -815,12 +815,11 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <strike/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -831,7 +830,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -843,8 +843,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3523,7 +3523,7 @@
         <v>6</v>
       </c>
       <c r="J32" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="21">

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13665" windowHeight="12315"/>
+    <workbookView windowWidth="21000" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="95">
   <si>
     <t>游戏ID</t>
   </si>
@@ -597,6 +597,30 @@
   </si>
   <si>
     <t>105100101|105100102|105100103|105100104</t>
+  </si>
+  <si>
+    <t>黄金帝国</t>
+  </si>
+  <si>
+    <t>105400101|105400102|105400103|105400104</t>
+  </si>
+  <si>
+    <t>招财猫</t>
+  </si>
+  <si>
+    <t>100800101|100800102|100800103|100800104</t>
+  </si>
+  <si>
+    <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>赏金大对决</t>
+  </si>
+  <si>
+    <t>105700101|105700102|105700103|105700104</t>
+  </si>
+  <si>
+    <t>极速糖果1000</t>
   </si>
 </sst>
 </file>
@@ -813,19 +837,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -837,14 +850,25 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1327,7 +1351,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1392,6 +1416,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1734,7 +1761,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -3523,7 +3550,7 @@
         <v>6</v>
       </c>
       <c r="J32" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="21">
@@ -3664,6 +3691,287 @@
         <v>1</v>
       </c>
       <c r="S34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A35" s="4">
+        <v>105400</v>
+      </c>
+      <c r="B35" s="4">
+        <v>105400001</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I35" s="4">
+        <v>5</v>
+      </c>
+      <c r="J35" s="4">
+        <v>6</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="21">
+        <v>1</v>
+      </c>
+      <c r="M35" s="21">
+        <v>1</v>
+      </c>
+      <c r="N35" s="4">
+        <v>20</v>
+      </c>
+      <c r="O35" s="4">
+        <v>1</v>
+      </c>
+      <c r="P35" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>1</v>
+      </c>
+      <c r="R35" s="13">
+        <v>1</v>
+      </c>
+      <c r="S35" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A36" s="4">
+        <v>100800</v>
+      </c>
+      <c r="B36" s="4">
+        <v>100800001</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="20">
+        <v>0</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="I36" s="4">
+        <v>6</v>
+      </c>
+      <c r="J36" s="4">
+        <v>6</v>
+      </c>
+      <c r="L36" s="21">
+        <v>1</v>
+      </c>
+      <c r="M36" s="21">
+        <v>1</v>
+      </c>
+      <c r="N36" s="4">
+        <v>20</v>
+      </c>
+      <c r="O36" s="4">
+        <v>1</v>
+      </c>
+      <c r="P36" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>1</v>
+      </c>
+      <c r="R36" s="13">
+        <v>1</v>
+      </c>
+      <c r="S36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A37" s="4">
+        <v>105300</v>
+      </c>
+      <c r="B37" s="4">
+        <v>105300001</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4">
+        <v>5</v>
+      </c>
+      <c r="J37" s="4">
+        <v>5</v>
+      </c>
+      <c r="L37" s="21">
+        <v>1</v>
+      </c>
+      <c r="M37" s="21">
+        <v>1</v>
+      </c>
+      <c r="N37" s="4">
+        <v>20</v>
+      </c>
+      <c r="O37" s="4">
+        <v>1</v>
+      </c>
+      <c r="P37" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>1</v>
+      </c>
+      <c r="R37" s="13">
+        <v>1</v>
+      </c>
+      <c r="S37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A38" s="4">
+        <v>105700</v>
+      </c>
+      <c r="B38" s="4">
+        <v>105700001</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="20">
+        <v>0</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="4">
+        <v>6</v>
+      </c>
+      <c r="J38" s="4">
+        <v>5</v>
+      </c>
+      <c r="L38" s="21">
+        <v>1</v>
+      </c>
+      <c r="M38" s="21">
+        <v>1</v>
+      </c>
+      <c r="N38" s="4">
+        <v>20</v>
+      </c>
+      <c r="O38" s="4">
+        <v>1</v>
+      </c>
+      <c r="P38" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>1</v>
+      </c>
+      <c r="R38" s="13">
+        <v>1</v>
+      </c>
+      <c r="S38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A39" s="4">
+        <v>105800</v>
+      </c>
+      <c r="B39" s="4">
+        <v>105800001</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="20">
+        <v>0</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" s="3">
+        <v>105800001</v>
+      </c>
+      <c r="I39" s="4">
+        <v>7</v>
+      </c>
+      <c r="J39" s="4">
+        <v>7</v>
+      </c>
+      <c r="L39" s="21">
+        <v>1</v>
+      </c>
+      <c r="M39" s="21">
+        <v>1</v>
+      </c>
+      <c r="N39" s="4">
+        <v>20</v>
+      </c>
+      <c r="O39" s="4">
+        <v>1</v>
+      </c>
+      <c r="P39" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>1</v>
+      </c>
+      <c r="R39" s="13">
+        <v>1</v>
+      </c>
+      <c r="S39" s="4">
         <v>1</v>
       </c>
     </row>
